--- a/generated/teacher_teacher_similarity.xlsx
+++ b/generated/teacher_teacher_similarity.xlsx
@@ -425,45 +425,2697 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>山田太郎</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>鈴木花子</t>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>繆瑩</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>有馬澄佳</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>イリチュ美佳</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>志田洋平</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>大久保正勝</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>張勇兵</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>上市秀雄</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>奥島真一郎</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>八森正泰</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>原田信行</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>藤井さやか</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>木下陽平</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>作道真理</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>髙橋裕紀</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>大西正輝</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>岡本直久</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>山田太郎</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.000000357627869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3665395379066467</v>
+        <v>0.8524669408798218</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8686813712120056</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9127810001373291</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9104170799255371</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9211149215698242</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8875312805175781</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8951934576034546</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8302707672119141</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9121062755584717</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9243653416633606</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9101786017417908</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.899531364440918</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8957887887954712</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.9101829528808594</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8336291313171387</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8343381881713867</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8883686065673828</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.9235917329788208</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.8883249163627625</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8823716640472412</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9374822974205017</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8960747122764587</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8949880599975586</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.902890682220459</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.8865189552307129</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8228821754455566</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.9079517722129822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>鈴木花子</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3665395379066467</v>
+        <v>0.8524669408798218</v>
       </c>
       <c r="C3" t="n">
+        <v>0.9999998807907104</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.866452157497406</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8364723920822144</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8491685390472412</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8560552597045898</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8405088782310486</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8631153702735901</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8289872407913208</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8384642601013184</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8597980737686157</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8446515202522278</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8732755780220032</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8553780317306519</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8673862218856812</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.8335090279579163</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8175127506256104</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8419703245162964</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.849434494972229</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.852882981300354</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8303762078285217</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.8576647043228149</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8387265801429749</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.849388599395752</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.8651005029678345</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.869402289390564</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8341293931007385</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8390929102897644</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.8686813712120056</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.866452157497406</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9999998807907104</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8476735353469849</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8546265363693237</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8511085510253906</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8565835952758789</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8535363674163818</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8349167704582214</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8530595898628235</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8679365515708923</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8521715402603149</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8850944638252258</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8547224402427673</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8733971118927002</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8369334936141968</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8352609276771545</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8449867963790894</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8615514039993286</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8583704233169556</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8407629728317261</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.8699272274971008</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8437125682830811</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8563985824584961</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.8508414030075073</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.8713870048522949</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8330405950546265</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.8458732962608337</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>繆瑩</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9127810001373291</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8364723920822144</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8476735353469849</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.000000238418579</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8988659381866455</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9047038555145264</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8700436353683472</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8900558352470398</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8357346057891846</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.908711850643158</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9142202734947205</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8921328783035278</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8772107362747192</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8865797519683838</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.893433153629303</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8382150530815125</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8337386846542358</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8785125017166138</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9174599647521973</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.8848069906234741</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8593936562538147</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.916956901550293</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.887496292591095</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.8836581707000732</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.8884457349777222</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.8731697797775269</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8222305178642273</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8859279155731201</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>有馬澄佳</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9104170799255371</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8491685390472412</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8546265363693237</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8988659381866455</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9213030338287354</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8774892091751099</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8921396732330322</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8341986536979675</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8980830311775208</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9284849166870117</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8996177911758423</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8997952938079834</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8863776922225952</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8930953741073608</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.8307888507843018</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.8262513875961304</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8723194599151611</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8920542001724243</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.8831583261489868</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8482007384300232</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9117148518562317</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.8778378963470459</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.8872561454772949</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.8881779313087463</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.8854338526725769</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8245714902877808</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8842787742614746</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>イリチュ美佳</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9211149215698242</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8560552597045898</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8511085510253906</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9047038555145264</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9213030338287354</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8846272230148315</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9021725654602051</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8370206356048584</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9011684060096741</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9326138496398926</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.912848949432373</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8978878259658813</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.913224458694458</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8969775438308716</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8332059383392334</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8429336547851562</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8932348489761353</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9090330600738525</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.9008340835571289</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8653336763381958</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9174145460128784</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8955031633377075</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.8974261283874512</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.901455283164978</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.8972249031066895</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8328536748886108</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8862299919128418</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>志田洋平</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8875312805175781</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8405088782310486</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8565835952758789</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8700436353683472</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8774892091751099</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8846272230148315</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9999999403953552</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8745768666267395</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8441516160964966</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8788844347000122</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8941791653633118</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.884702742099762</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8881736397743225</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.908638596534729</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8885284662246704</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.8626000881195068</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8523857593536377</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8663286566734314</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8732837438583374</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.8703348636627197</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.8698242902755737</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8939296007156372</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.9046574831008911</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.879912257194519</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.8807768225669861</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.8693918585777283</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8496972322463989</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.8852790594100952</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>大久保正勝</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8951934576034546</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8631153702735901</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8535363674163818</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8900558352470398</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8921396732330322</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9021725654602051</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8745768666267395</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9999998807907104</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8434658050537109</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8714597821235657</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8997255563735962</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9117185473442078</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8979413509368896</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8949402570724487</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8861508369445801</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.8431073427200317</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8250465393066406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9006692171096802</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8911222219467163</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9054946899414062</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.8542855381965637</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9036498665809631</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.8795552849769592</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.8782399892807007</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.9112921357154846</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.8981694579124451</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8332096338272095</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.8896946907043457</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8302707672119141</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8289872407913208</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8349167704582214</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8357346057891846</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8341986536979675</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8370206356048584</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8441516160964966</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8434658050537109</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.00000011920929</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8303543329238892</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8460994958877563</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8435174226760864</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8366104364395142</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8362822532653809</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8321028351783752</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.9398021697998047</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9279340505599976</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8274298906326294</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.8336665034294128</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.8291482925415039</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8119673728942871</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.8405823707580566</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8251742124557495</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.827221155166626</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.8362271785736084</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.8342908024787903</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8821119070053101</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.8334486484527588</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>張勇兵</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9121062755584717</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8384642601013184</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8530595898628235</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.908711850643158</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8980830311775208</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9011684060096741</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8788844347000122</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8714597821235657</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8303543329238892</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.9999998807907104</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.905300498008728</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8927918672561646</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8723720908164978</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8869379758834839</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.9071863889694214</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.8479938507080078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8295843601226807</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.8710378408432007</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9023727178573608</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.8823256492614746</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8778689503669739</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9212817549705505</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.9014301300048828</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.9006924629211426</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.8756319880485535</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.8725012540817261</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.817221999168396</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.8965610265731812</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9243653416633606</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8597980737686157</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8679365515708923</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9142202734947205</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9284849166870117</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9326138496398926</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8941791653633118</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8997255563735962</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8460994958877563</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.905300498008728</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.00000011920929</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9193600416183472</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.9056236743927002</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9161235094070435</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9211479425430298</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.8533174991607666</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8354157209396362</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8914902806282043</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9103498458862305</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.9135844111442566</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8813762068748474</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9336406588554382</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9012442827224731</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.9059131145477295</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.9170732498168945</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.9002515077590942</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.833482027053833</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.9069328904151917</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>上市秀雄</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.9101786017417908</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8446515202522278</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8521715402603149</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8921328783035278</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8996177911758423</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.912848949432373</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.884702742099762</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9117185473442078</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8435174226760864</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8927918672561646</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9193600416183472</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8829388618469238</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.9241669178009033</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.915088951587677</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.8506760597229004</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8384671211242676</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.903888463973999</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8981676697731018</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.9168130159378052</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.8776522874832153</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.9148710370063782</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.8846296072006226</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.9190843105316162</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.8958896398544312</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.9150595664978027</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8425793051719666</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.9070229530334473</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.899531364440918</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8732755780220032</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8850944638252258</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8772107362747192</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8997952938079834</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8978878259658813</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8881736397743225</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8979413509368896</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8366104364395142</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8723720908164978</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9056236743927002</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8829388618469238</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8864870071411133</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8959065675735474</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.8447829484939575</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8360897898674011</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.8714480400085449</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.886219322681427</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.882748007774353</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8582971096038818</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8976263999938965</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8827852010726929</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.8751000165939331</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.9021697044372559</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.882618248462677</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8427293300628662</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.8750876188278198</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8957887887954712</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8553780317306519</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8547224402427673</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8865797519683838</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8863776922225952</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.913224458694458</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.908638596534729</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8949402570724487</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8362822532653809</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8869379758834839</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9161235094070435</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9241669178009033</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8864870071411133</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.000000238418579</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9104539155960083</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.8529775142669678</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8333733081817627</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.8957282304763794</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.8940631151199341</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.9011842012405396</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.883326530456543</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.9150640964508057</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.8991782665252686</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.9066460132598877</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.9023823738098145</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.8968706130981445</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8355642557144165</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.8956929445266724</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9101829528808594</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8673862218856812</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8733971118927002</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.893433153629303</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8930953741073608</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8969775438308716</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8885284662246704</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8861508369445801</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8321028351783752</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.9071863889694214</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9211479425430298</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.915088951587677</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8959065675735474</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.9104539155960083</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.000000476837158</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.847346305847168</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8235707879066467</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.8813589215278625</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.9019486308097839</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.8909293413162231</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8984862565994263</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9150462746620178</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8876562118530273</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.9192123413085938</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.8921593427658081</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.8949098587036133</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8217706680297852</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.9206446409225464</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.8336291313171387</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8335090279579163</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8369334936141968</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8382150530815125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8307888507843018</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8332059383392334</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8626000881195068</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8431073427200317</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9398021697998047</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8479938507080078</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8533174991607666</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8506760597229004</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8447829484939575</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8529775142669678</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.847346305847168</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0.9999997615814209</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9344090223312378</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.8416507244110107</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8364711999893188</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.8427741527557373</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8257176876068115</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.8499367833137512</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8467764854431152</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8399659395217896</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.8588438034057617</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.8345358371734619</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8854494094848633</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.8531848192214966</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.8343381881713867</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8175127506256104</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8352609276771545</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8337386846542358</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8262513875961304</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8429336547851562</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8523857593536377</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8250465393066406</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9279340505599976</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.8295843601226807</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8354157209396362</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8384671211242676</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.8360897898674011</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8333733081817627</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8235707879066467</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.9344090223312378</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9999998807907104</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8214161396026611</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.8266108632087708</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.8321260213851929</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.7994647622108459</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.828365683555603</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.8305207490921021</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.8186362981796265</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.824305534362793</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.8239538073539734</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.897186279296875</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.8272530436515808</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>奥島真一郎</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.8883686065673828</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8419703245162964</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8449867963790894</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8785125017166138</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8723194599151611</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8932348489761353</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8663286566734314</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9006692171096802</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8274298906326294</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8710378408432007</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8914902806282043</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.903888463973999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8714480400085449</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8957282304763794</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8813589215278625</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8416507244110107</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.8214161396026611</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.9999999403953552</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.8915920257568359</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.9023893475532532</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.8749428987503052</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.8950690031051636</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8799763917922974</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.8868472576141357</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.9093791246414185</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.8760640621185303</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8358195424079895</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.8798643350601196</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>八森正泰</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9235917329788208</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.849434494972229</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8615514039993286</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9174599647521973</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8920542001724243</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9090330600738525</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8732837438583374</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8911222219467163</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8336665034294128</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.9023727178573608</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.9103498458862305</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8981676697731018</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.886219322681427</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8940631151199341</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9019486308097839</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8364711999893188</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.8266108632087708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8915920257568359</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.9999998807907104</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.8907653093338013</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8683456182479858</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9276247620582581</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.8842158317565918</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.8886278867721558</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.8980714082717896</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.8677718639373779</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8305901885032654</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.8808428049087524</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>原田信行</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.8883249163627625</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.852882981300354</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8583704233169556</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8848069906234741</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8831583261489868</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9008340835571289</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8703348636627197</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9054946899414062</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8291482925415039</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8823256492614746</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9135844111442566</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9168130159378052</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.882748007774353</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9011842012405396</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.8909293413162231</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8427741527557373</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.8321260213851929</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9023893475532532</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.8907653093338013</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9999998211860657</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.8583604097366333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9062308073043823</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.8727902173995972</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.8853163719177246</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.9058578014373779</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.9010766744613647</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8331699967384338</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.8845592737197876</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>藤井さやか</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.8823716640472412</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8303762078285217</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.8407629728317261</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8593936562538147</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8482007384300232</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8653336763381958</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8698242902755737</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8542855381965637</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8119673728942871</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8778689503669739</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.8813762068748474</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.8776522874832153</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8582971096038818</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.883326530456543</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8984862565994263</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.8257176876068115</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.7994647622108459</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.8749428987503052</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.8683456182479858</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8583604097366333</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.00000011920929</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.8874898552894592</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.8852674961090088</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.9022369980812073</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.8617401719093323</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.8580697774887085</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8172383308410645</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.9014617800712585</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9374822974205017</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8576647043228149</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8699272274971008</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.916956901550293</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9117148518562317</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9174145460128784</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.8939296007156372</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9036498665809631</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8405823707580566</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9212817549705505</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.9336406588554382</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9148710370063782</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8976263999938965</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.9150640964508057</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9150462746620178</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.8499367833137512</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.828365683555603</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.8950690031051636</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.9276247620582581</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.9062308073043823</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.8874898552894592</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.8961538076400757</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.9051117897033691</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.9058386087417603</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.8993154168128967</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.8257131576538086</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.9100641012191772</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>木下陽平</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.8960747122764587</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8387265801429749</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8437125682830811</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.887496292591095</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8778378963470459</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8955031633377075</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9046574831008911</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8795552849769592</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8251742124557495</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.9014301300048828</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9012442827224731</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.8846296072006226</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.8827852010726929</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8991782665252686</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.8876562118530273</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.8467764854431152</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.8305207490921021</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.8799763917922974</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.8842158317565918</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.8727902173995972</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.8852674961090088</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.8961538076400757</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.9999999403953552</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.8765764236450195</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.8843064308166504</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8600653409957886</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.829736590385437</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.8958688378334045</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.8949880599975586</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.849388599395752</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8563985824584961</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8836581707000732</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8872561454772949</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8974261283874512</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.879912257194519</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8782399892807007</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.827221155166626</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9006924629211426</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9059131145477295</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9190843105316162</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.8751000165939331</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9066460132598877</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9192123413085938</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8399659395217896</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.8186362981796265</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.8868472576141357</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.8886278867721558</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.8853163719177246</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.9022369980812073</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.9051117897033691</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.8765764236450195</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.9999998211860657</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.8873841762542725</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.8847143054008484</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.8345935344696045</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.902002215385437</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>作道真理</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.902890682220459</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8651005029678345</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.8508414030075073</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8884457349777222</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8881779313087463</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.901455283164978</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8807768225669861</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9112921357154846</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8362271785736084</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8756319880485535</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.9170732498168945</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8958896398544312</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.9021697044372559</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.9023823738098145</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.8921593427658081</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.8588438034057617</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.824305534362793</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.9093791246414185</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.8980714082717896</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.9058578014373779</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.8617401719093323</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9058386087417603</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.8843064308166504</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.8873841762542725</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.8854634761810303</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.8346238136291504</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.8862978219985962</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>髙橋裕紀</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.8865189552307129</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.869402289390564</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8713870048522949</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8731697797775269</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8854338526725769</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8972249031066895</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8693918585777283</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8981694579124451</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8342908024787903</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8725012540817261</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9002515077590942</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.9150595664978027</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.882618248462677</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8968706130981445</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.8949098587036133</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.8345358371734619</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.8239538073539734</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.8760640621185303</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.8677718639373779</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.9010766744613647</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.8580697774887085</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.8993154168128967</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.8600653409957886</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.8847143054008484</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.8854634761810303</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.000000357627869</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.8222634196281433</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.8883249759674072</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>大西正輝</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.8228821754455566</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8341293931007385</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.8330405950546265</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8222305178642273</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8245714902877808</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8328536748886108</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8496972322463989</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8332096338272095</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8821119070053101</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.817221999168396</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.833482027053833</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.8425793051719666</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.8427293300628662</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8355642557144165</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.8217706680297852</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8854494094848633</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.897186279296875</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.8358195424079895</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.8305901885032654</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.8331699967384338</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.8172383308410645</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.8257131576538086</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.829736590385437</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.8345935344696045</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.8346238136291504</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.8222634196281433</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.00000011920929</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.8268973827362061</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>岡本直久</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.9079517722129822</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8390929102897644</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8458732962608337</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8859279155731201</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.8842787742614746</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.8862299919128418</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.8852790594100952</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8896946907043457</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8334486484527588</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8965610265731812</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.9069328904151917</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.9070229530334473</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.8750876188278198</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.8956929445266724</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9206446409225464</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.8531848192214966</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8272530436515808</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.8798643350601196</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.8808428049087524</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.8845592737197876</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9014617800712585</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.9100641012191772</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.8958688378334045</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.902002215385437</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.8862978219985962</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.8883249759674072</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.8268973827362061</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/generated/teacher_teacher_similarity.xlsx
+++ b/generated/teacher_teacher_similarity.xlsx
@@ -577,88 +577,88 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.000000357627869</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8524669408798218</v>
+        <v>0.8524665236473083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8686813712120056</v>
+        <v>0.8686808347702026</v>
       </c>
       <c r="E2" t="n">
         <v>0.9127810001373291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9104170799255371</v>
+        <v>0.9104167222976685</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9211149215698242</v>
+        <v>0.9211148023605347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8875312805175781</v>
+        <v>0.887531042098999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8951934576034546</v>
+        <v>0.8951929211616516</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8302707672119141</v>
+        <v>0.8302701711654663</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9121062755584717</v>
+        <v>0.9121061563491821</v>
       </c>
       <c r="L2" t="n">
         <v>0.9243653416633606</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9101786017417908</v>
+        <v>0.9101783633232117</v>
       </c>
       <c r="N2" t="n">
-        <v>0.899531364440918</v>
+        <v>0.8995309472084045</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8957887887954712</v>
+        <v>0.8957883715629578</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9101829528808594</v>
+        <v>0.9101825952529907</v>
       </c>
       <c r="Q2" t="n">
         <v>0.8336291313171387</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8343381881713867</v>
+        <v>0.8343378305435181</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8883686065673828</v>
+        <v>0.8883687257766724</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9235917329788208</v>
+        <v>0.9235914945602417</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8883249163627625</v>
+        <v>0.8883245587348938</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8823716640472412</v>
+        <v>0.8823714256286621</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9374822974205017</v>
+        <v>0.9374818801879883</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8960747122764587</v>
+        <v>0.8960744142532349</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8949880599975586</v>
+        <v>0.8949875831604004</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.902890682220459</v>
+        <v>0.9028902053833008</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8865189552307129</v>
+        <v>0.8865185976028442</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8228821754455566</v>
+        <v>0.8228815793991089</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9079517722129822</v>
+        <v>0.9079517126083374</v>
       </c>
     </row>
     <row r="3">
@@ -668,88 +668,88 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8524669408798218</v>
+        <v>0.8524665236473083</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9999998807907104</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.866452157497406</v>
+        <v>0.8664517998695374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8364723920822144</v>
+        <v>0.8364719748497009</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8491685390472412</v>
+        <v>0.8491683602333069</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8560552597045898</v>
+        <v>0.8560551404953003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8405088782310486</v>
+        <v>0.8405083417892456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8631153702735901</v>
+        <v>0.8631149530410767</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8289872407913208</v>
+        <v>0.8289868235588074</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8384642601013184</v>
+        <v>0.8384640216827393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8597980737686157</v>
+        <v>0.8597980141639709</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8446515202522278</v>
+        <v>0.8446508646011353</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8732755780220032</v>
+        <v>0.8732753992080688</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8553780317306519</v>
+        <v>0.8553775548934937</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8673862218856812</v>
+        <v>0.8673859834671021</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8335090279579163</v>
+        <v>0.833509087562561</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8175127506256104</v>
+        <v>0.8175126314163208</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8419703245162964</v>
+        <v>0.8419700860977173</v>
       </c>
       <c r="T3" t="n">
-        <v>0.849434494972229</v>
+        <v>0.8494346141815186</v>
       </c>
       <c r="U3" t="n">
-        <v>0.852882981300354</v>
+        <v>0.8528826236724854</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8303762078285217</v>
+        <v>0.8303756713867188</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8576647043228149</v>
+        <v>0.8576644659042358</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8387265801429749</v>
+        <v>0.8387263417243958</v>
       </c>
       <c r="Y3" t="n">
         <v>0.849388599395752</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.8651005029678345</v>
+        <v>0.8651002049446106</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.869402289390564</v>
+        <v>0.8694019317626953</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8341293931007385</v>
+        <v>0.8341289758682251</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8390929102897644</v>
+        <v>0.8390926122665405</v>
       </c>
     </row>
     <row r="4">
@@ -759,88 +759,88 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8686813712120056</v>
+        <v>0.8686808347702026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.866452157497406</v>
+        <v>0.8664517998695374</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="E4" t="n">
         <v>0.8476735353469849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8546265363693237</v>
+        <v>0.8546262383460999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8511085510253906</v>
+        <v>0.851108193397522</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8565835952758789</v>
+        <v>0.8565832376480103</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8535363674163818</v>
+        <v>0.8535357713699341</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8349167704582214</v>
+        <v>0.834916353225708</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8530595898628235</v>
+        <v>0.8530595302581787</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8679365515708923</v>
+        <v>0.8679360151290894</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8521715402603149</v>
+        <v>0.8521713018417358</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8850944638252258</v>
+        <v>0.8850942254066467</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8547224402427673</v>
+        <v>0.8547220230102539</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8733971118927002</v>
+        <v>0.8733967542648315</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8369334936141968</v>
+        <v>0.836932897567749</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8352609276771545</v>
+        <v>0.835260808467865</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8449867963790894</v>
+        <v>0.8449864387512207</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8615514039993286</v>
+        <v>0.8615512847900391</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8583704233169556</v>
+        <v>0.858370304107666</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8407629728317261</v>
+        <v>0.8407632112503052</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8699272274971008</v>
+        <v>0.869926929473877</v>
       </c>
       <c r="X4" t="n">
         <v>0.8437125682830811</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8563985824584961</v>
+        <v>0.8563982248306274</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8508414030075073</v>
+        <v>0.850841224193573</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.8713870048522949</v>
+        <v>0.8713867664337158</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8330405950546265</v>
+        <v>0.8330402970314026</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8458732962608337</v>
+        <v>0.8458731174468994</v>
       </c>
     </row>
     <row r="5">
@@ -853,85 +853,85 @@
         <v>0.9127810001373291</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8364723920822144</v>
+        <v>0.8364719748497009</v>
       </c>
       <c r="D5" t="n">
         <v>0.8476735353469849</v>
       </c>
       <c r="E5" t="n">
-        <v>1.000000238418579</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8988659381866455</v>
+        <v>0.8988657593727112</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9047038555145264</v>
+        <v>0.9047037363052368</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8700436353683472</v>
+        <v>0.8700432777404785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8900558352470398</v>
+        <v>0.8900554776191711</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8357346057891846</v>
+        <v>0.8357341289520264</v>
       </c>
       <c r="K5" t="n">
-        <v>0.908711850643158</v>
+        <v>0.9087117910385132</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9142202734947205</v>
+        <v>0.9142200946807861</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8921328783035278</v>
+        <v>0.8921324014663696</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8772107362747192</v>
+        <v>0.8772101402282715</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8865797519683838</v>
+        <v>0.8865792751312256</v>
       </c>
       <c r="P5" t="n">
-        <v>0.893433153629303</v>
+        <v>0.8934330344200134</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8382150530815125</v>
+        <v>0.8382149934768677</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8337386846542358</v>
+        <v>0.8337384462356567</v>
       </c>
       <c r="S5" t="n">
         <v>0.8785125017166138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9174599647521973</v>
+        <v>0.917460024356842</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8848069906234741</v>
+        <v>0.8848065733909607</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8593936562538147</v>
+        <v>0.8593931794166565</v>
       </c>
       <c r="W5" t="n">
-        <v>0.916956901550293</v>
+        <v>0.9169570207595825</v>
       </c>
       <c r="X5" t="n">
-        <v>0.887496292591095</v>
+        <v>0.8874961733818054</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8836581707000732</v>
+        <v>0.8836584091186523</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8884457349777222</v>
+        <v>0.8884453773498535</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8731697797775269</v>
+        <v>0.8731695413589478</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8222305178642273</v>
+        <v>0.8222304582595825</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8859279155731201</v>
+        <v>0.8859280347824097</v>
       </c>
     </row>
     <row r="6">
@@ -941,88 +941,88 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9104170799255371</v>
+        <v>0.9104167222976685</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8491685390472412</v>
+        <v>0.8491683602333069</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8546265363693237</v>
+        <v>0.8546262383460999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8988659381866455</v>
+        <v>0.8988657593727112</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9213030338287354</v>
+        <v>0.9213026762008667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8774892091751099</v>
+        <v>0.8774891495704651</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8921396732330322</v>
+        <v>0.8921391367912292</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8341986536979675</v>
+        <v>0.834198534488678</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8980830311775208</v>
+        <v>0.8980823755264282</v>
       </c>
       <c r="L6" t="n">
         <v>0.9284849166870117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8996177911758423</v>
+        <v>0.8996173739433289</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8997952938079834</v>
+        <v>0.8997945785522461</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8863776922225952</v>
+        <v>0.8863773345947266</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8930953741073608</v>
+        <v>0.893095076084137</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8307888507843018</v>
+        <v>0.8307887315750122</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8262513875961304</v>
+        <v>0.8262505531311035</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8723194599151611</v>
+        <v>0.8723193407058716</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8920542001724243</v>
+        <v>0.8920536637306213</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8831583261489868</v>
+        <v>0.8831580877304077</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8482007384300232</v>
+        <v>0.8482003808021545</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9117148518562317</v>
+        <v>0.911715030670166</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8778378963470459</v>
+        <v>0.8778374195098877</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8872561454772949</v>
+        <v>0.8872556090354919</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8881779313087463</v>
+        <v>0.8881773948669434</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8854338526725769</v>
+        <v>0.8854333162307739</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8245714902877808</v>
+        <v>0.8245711326599121</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8842787742614746</v>
+        <v>0.8842782974243164</v>
       </c>
     </row>
     <row r="7">
@@ -1032,88 +1032,88 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9211149215698242</v>
+        <v>0.9211148023605347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8560552597045898</v>
+        <v>0.8560551404953003</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8511085510253906</v>
+        <v>0.851108193397522</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9047038555145264</v>
+        <v>0.9047037363052368</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9213030338287354</v>
+        <v>0.9213026762008667</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8846272230148315</v>
+        <v>0.8846269845962524</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9021725654602051</v>
+        <v>0.9021722078323364</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8370206356048584</v>
+        <v>0.8370207548141479</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9011684060096741</v>
+        <v>0.9011682271957397</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9326138496398926</v>
+        <v>0.9326137900352478</v>
       </c>
       <c r="M7" t="n">
-        <v>0.912848949432373</v>
+        <v>0.9128487110137939</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8978878259658813</v>
+        <v>0.8978871703147888</v>
       </c>
       <c r="O7" t="n">
-        <v>0.913224458694458</v>
+        <v>0.9132239818572998</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8969775438308716</v>
+        <v>0.8969773054122925</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8332059383392334</v>
+        <v>0.8332055807113647</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8429336547851562</v>
+        <v>0.8429340124130249</v>
       </c>
       <c r="S7" t="n">
         <v>0.8932348489761353</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9090330600738525</v>
+        <v>0.9090328812599182</v>
       </c>
       <c r="U7" t="n">
         <v>0.9008340835571289</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8653336763381958</v>
+        <v>0.8653331995010376</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9174145460128784</v>
+        <v>0.9174143671989441</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8955031633377075</v>
+        <v>0.8955028057098389</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8974261283874512</v>
+        <v>0.8974260687828064</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.901455283164978</v>
+        <v>0.9014550447463989</v>
       </c>
       <c r="AA7" t="n">
         <v>0.8972249031066895</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8328536748886108</v>
+        <v>0.8328535556793213</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8862299919128418</v>
+        <v>0.8862297534942627</v>
       </c>
     </row>
     <row r="8">
@@ -1123,46 +1123,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8875312805175781</v>
+        <v>0.887531042098999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8405088782310486</v>
+        <v>0.8405083417892456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8565835952758789</v>
+        <v>0.8565832376480103</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8700436353683472</v>
+        <v>0.8700432777404785</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8774892091751099</v>
+        <v>0.8774891495704651</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8846272230148315</v>
+        <v>0.8846269845962524</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9999999403953552</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8745768666267395</v>
+        <v>0.8745768070220947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8441516160964966</v>
+        <v>0.844151496887207</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8788844347000122</v>
+        <v>0.8788841366767883</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8941791653633118</v>
+        <v>0.8941789865493774</v>
       </c>
       <c r="M8" t="n">
-        <v>0.884702742099762</v>
+        <v>0.8847023248672485</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8881736397743225</v>
+        <v>0.8881731033325195</v>
       </c>
       <c r="O8" t="n">
-        <v>0.908638596534729</v>
+        <v>0.9086384773254395</v>
       </c>
       <c r="P8" t="n">
         <v>0.8885284662246704</v>
@@ -1171,40 +1171,40 @@
         <v>0.8626000881195068</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8523857593536377</v>
+        <v>0.8523854613304138</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8663286566734314</v>
+        <v>0.8663284778594971</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8732837438583374</v>
+        <v>0.8732834458351135</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8703348636627197</v>
+        <v>0.8703346252441406</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8698242902755737</v>
+        <v>0.8698241710662842</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8939296007156372</v>
+        <v>0.8939295411109924</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9046574831008911</v>
+        <v>0.9046571850776672</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.879912257194519</v>
+        <v>0.8799123764038086</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8807768225669861</v>
+        <v>0.8807762861251831</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8693918585777283</v>
+        <v>0.8693917989730835</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8496972322463989</v>
+        <v>0.8496968746185303</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.8852790594100952</v>
+        <v>0.8852788209915161</v>
       </c>
     </row>
     <row r="9">
@@ -1214,88 +1214,88 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8951934576034546</v>
+        <v>0.8951929211616516</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8631153702735901</v>
+        <v>0.8631149530410767</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8535363674163818</v>
+        <v>0.8535357713699341</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8900558352470398</v>
+        <v>0.8900554776191711</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8921396732330322</v>
+        <v>0.8921391367912292</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9021725654602051</v>
+        <v>0.9021722078323364</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8745768666267395</v>
+        <v>0.8745768070220947</v>
       </c>
       <c r="I9" t="n">
         <v>0.9999998807907104</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8434658050537109</v>
+        <v>0.8434652090072632</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8714597821235657</v>
+        <v>0.8714591860771179</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8997255563735962</v>
+        <v>0.8997251987457275</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9117185473442078</v>
+        <v>0.9117178916931152</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8979413509368896</v>
+        <v>0.8979407548904419</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8949402570724487</v>
+        <v>0.8949397802352905</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8861508369445801</v>
+        <v>0.8861502408981323</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8431073427200317</v>
+        <v>0.843107283115387</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8250465393066406</v>
+        <v>0.8250464200973511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9006692171096802</v>
+        <v>0.900668740272522</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8911222219467163</v>
+        <v>0.8911218047142029</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9054946899414062</v>
+        <v>0.9054938554763794</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8542855381965637</v>
+        <v>0.8542848825454712</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9036498665809631</v>
+        <v>0.9036496877670288</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8795552849769592</v>
+        <v>0.8795550465583801</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8782399892807007</v>
+        <v>0.878239631652832</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9112921357154846</v>
+        <v>0.9112923145294189</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8981694579124451</v>
+        <v>0.8981688618659973</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8332096338272095</v>
+        <v>0.8332093954086304</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8896946907043457</v>
+        <v>0.8896943330764771</v>
       </c>
     </row>
     <row r="10">
@@ -1305,85 +1305,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8302707672119141</v>
+        <v>0.8302701711654663</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8289872407913208</v>
+        <v>0.8289868235588074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8349167704582214</v>
+        <v>0.834916353225708</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8357346057891846</v>
+        <v>0.8357341289520264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8341986536979675</v>
+        <v>0.834198534488678</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8370206356048584</v>
+        <v>0.8370207548141479</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8441516160964966</v>
+        <v>0.844151496887207</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8434658050537109</v>
+        <v>0.8434652090072632</v>
       </c>
       <c r="J10" t="n">
-        <v>1.00000011920929</v>
+        <v>1.000000357627869</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8303543329238892</v>
+        <v>0.830353856086731</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8460994958877563</v>
+        <v>0.8460994362831116</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8435174226760864</v>
+        <v>0.8435173034667969</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8366104364395142</v>
+        <v>0.8366098999977112</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8362822532653809</v>
+        <v>0.8362821340560913</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8321028351783752</v>
+        <v>0.8321027755737305</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9398021697998047</v>
+        <v>0.9398022890090942</v>
       </c>
       <c r="R10" t="n">
         <v>0.9279340505599976</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8274298906326294</v>
+        <v>0.8274297714233398</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8336665034294128</v>
+        <v>0.8336663246154785</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8291482925415039</v>
+        <v>0.8291481733322144</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8119673728942871</v>
+        <v>0.8119672536849976</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8405823707580566</v>
+        <v>0.8405822515487671</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8251742124557495</v>
+        <v>0.8251737356185913</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.827221155166626</v>
+        <v>0.8272209167480469</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8362271785736084</v>
+        <v>0.8362268209457397</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8342908024787903</v>
+        <v>0.8342905044555664</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8821119070053101</v>
+        <v>0.8821115493774414</v>
       </c>
       <c r="AC10" t="n">
         <v>0.8334486484527588</v>
@@ -1396,88 +1396,88 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9121062755584717</v>
+        <v>0.9121061563491821</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8384642601013184</v>
+        <v>0.8384640216827393</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8530595898628235</v>
+        <v>0.8530595302581787</v>
       </c>
       <c r="E11" t="n">
-        <v>0.908711850643158</v>
+        <v>0.9087117910385132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8980830311775208</v>
+        <v>0.8980823755264282</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9011684060096741</v>
+        <v>0.9011682271957397</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8788844347000122</v>
+        <v>0.8788841366767883</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8714597821235657</v>
+        <v>0.8714591860771179</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8303543329238892</v>
+        <v>0.830353856086731</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9999998807907104</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.905300498008728</v>
+        <v>0.9053002595901489</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8927918672561646</v>
+        <v>0.8927915096282959</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8723720908164978</v>
+        <v>0.8723717927932739</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8869379758834839</v>
+        <v>0.8869377970695496</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9071863889694214</v>
+        <v>0.9071865081787109</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8479938507080078</v>
+        <v>0.8479936718940735</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8295843601226807</v>
+        <v>0.8295843005180359</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8710378408432007</v>
+        <v>0.8710376024246216</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9023727178573608</v>
+        <v>0.9023722410202026</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8823256492614746</v>
+        <v>0.8823255300521851</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8778689503669739</v>
+        <v>0.87786865234375</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9212817549705505</v>
+        <v>0.9212815165519714</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9014301300048828</v>
+        <v>0.9014304876327515</v>
       </c>
       <c r="Y11" t="n">
         <v>0.9006924629211426</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8756319880485535</v>
+        <v>0.8756316900253296</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.8725012540817261</v>
+        <v>0.8725007772445679</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.817221999168396</v>
+        <v>0.8172218799591064</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8965610265731812</v>
+        <v>0.8965604901313782</v>
       </c>
     </row>
     <row r="12">
@@ -1490,85 +1490,85 @@
         <v>0.9243653416633606</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8597980737686157</v>
+        <v>0.8597980141639709</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8679365515708923</v>
+        <v>0.8679360151290894</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9142202734947205</v>
+        <v>0.9142200946807861</v>
       </c>
       <c r="F12" t="n">
         <v>0.9284849166870117</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9326138496398926</v>
+        <v>0.9326137900352478</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8941791653633118</v>
+        <v>0.8941789865493774</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8997255563735962</v>
+        <v>0.8997251987457275</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8460994958877563</v>
+        <v>0.8460994362831116</v>
       </c>
       <c r="K12" t="n">
-        <v>0.905300498008728</v>
+        <v>0.9053002595901489</v>
       </c>
       <c r="L12" t="n">
-        <v>1.00000011920929</v>
+        <v>1.000000357627869</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9193600416183472</v>
+        <v>0.9193594455718994</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9056236743927002</v>
+        <v>0.9056235551834106</v>
       </c>
       <c r="O12" t="n">
         <v>0.9161235094070435</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9211479425430298</v>
+        <v>0.9211475849151611</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8533174991607666</v>
+        <v>0.8533173799514771</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8354157209396362</v>
+        <v>0.8354154825210571</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8914902806282043</v>
+        <v>0.8914898633956909</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9103498458862305</v>
+        <v>0.9103497862815857</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9135844111442566</v>
+        <v>0.9135845899581909</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8813762068748474</v>
+        <v>0.8813762664794922</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9336406588554382</v>
+        <v>0.9336405992507935</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9012442827224731</v>
+        <v>0.9012448191642761</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.9059131145477295</v>
+        <v>0.9059126973152161</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.9170732498168945</v>
+        <v>0.9170726537704468</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.9002515077590942</v>
+        <v>0.9002512693405151</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.833482027053833</v>
+        <v>0.8334816098213196</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.9069328904151917</v>
+        <v>0.9069327116012573</v>
       </c>
     </row>
     <row r="13">
@@ -1578,73 +1578,73 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9101786017417908</v>
+        <v>0.9101783633232117</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8446515202522278</v>
+        <v>0.8446508646011353</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8521715402603149</v>
+        <v>0.8521713018417358</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8921328783035278</v>
+        <v>0.8921324014663696</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8996177911758423</v>
+        <v>0.8996173739433289</v>
       </c>
       <c r="G13" t="n">
-        <v>0.912848949432373</v>
+        <v>0.9128487110137939</v>
       </c>
       <c r="H13" t="n">
-        <v>0.884702742099762</v>
+        <v>0.8847023248672485</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9117185473442078</v>
+        <v>0.9117178916931152</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8435174226760864</v>
+        <v>0.8435173034667969</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8927918672561646</v>
+        <v>0.8927915096282959</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9193600416183472</v>
+        <v>0.9193594455718994</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8829388618469238</v>
+        <v>0.8829382061958313</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9241669178009033</v>
+        <v>0.9241664409637451</v>
       </c>
       <c r="P13" t="n">
-        <v>0.915088951587677</v>
+        <v>0.9150885343551636</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8506760597229004</v>
+        <v>0.8506755828857422</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8384671211242676</v>
+        <v>0.8384667634963989</v>
       </c>
       <c r="S13" t="n">
-        <v>0.903888463973999</v>
+        <v>0.9038882851600647</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8981676697731018</v>
+        <v>0.8981672525405884</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9168130159378052</v>
+        <v>0.9168126583099365</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8776522874832153</v>
+        <v>0.8776520490646362</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9148710370063782</v>
+        <v>0.9148703813552856</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8846296072006226</v>
+        <v>0.8846292495727539</v>
       </c>
       <c r="Y13" t="n">
         <v>0.9190843105316162</v>
@@ -1653,13 +1653,13 @@
         <v>0.8958896398544312</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9150595664978027</v>
+        <v>0.9150591492652893</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8425793051719666</v>
+        <v>0.8425792455673218</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.9070229530334473</v>
+        <v>0.9070228338241577</v>
       </c>
     </row>
     <row r="14">
@@ -1669,88 +1669,88 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.899531364440918</v>
+        <v>0.8995309472084045</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8732755780220032</v>
+        <v>0.8732753992080688</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8850944638252258</v>
+        <v>0.8850942254066467</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8772107362747192</v>
+        <v>0.8772101402282715</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8997952938079834</v>
+        <v>0.8997945785522461</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8978878259658813</v>
+        <v>0.8978871703147888</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8881736397743225</v>
+        <v>0.8881731033325195</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8979413509368896</v>
+        <v>0.8979407548904419</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8366104364395142</v>
+        <v>0.8366098999977112</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8723720908164978</v>
+        <v>0.8723717927932739</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9056236743927002</v>
+        <v>0.9056235551834106</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8829388618469238</v>
+        <v>0.8829382061958313</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8864870071411133</v>
+        <v>0.8864867687225342</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8959065675735474</v>
+        <v>0.8959063291549683</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8447829484939575</v>
+        <v>0.844782829284668</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8360897898674011</v>
+        <v>0.8360894918441772</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8714480400085449</v>
+        <v>0.8714476823806763</v>
       </c>
       <c r="T14" t="n">
-        <v>0.886219322681427</v>
+        <v>0.8862186670303345</v>
       </c>
       <c r="U14" t="n">
-        <v>0.882748007774353</v>
+        <v>0.8827479481697083</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8582971096038818</v>
+        <v>0.8582968711853027</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8976263999938965</v>
+        <v>0.8976262807846069</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8827852010726929</v>
+        <v>0.8827848434448242</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8751000165939331</v>
+        <v>0.8750998973846436</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.9021697044372559</v>
+        <v>0.9021689891815186</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.882618248462677</v>
+        <v>0.8826179504394531</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8427293300628662</v>
+        <v>0.842729389667511</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.8750876188278198</v>
+        <v>0.8750870227813721</v>
       </c>
     </row>
     <row r="15">
@@ -1760,88 +1760,88 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8957887887954712</v>
+        <v>0.8957883715629578</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8553780317306519</v>
+        <v>0.8553775548934937</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8547224402427673</v>
+        <v>0.8547220230102539</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8865797519683838</v>
+        <v>0.8865792751312256</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8863776922225952</v>
+        <v>0.8863773345947266</v>
       </c>
       <c r="G15" t="n">
-        <v>0.913224458694458</v>
+        <v>0.9132239818572998</v>
       </c>
       <c r="H15" t="n">
-        <v>0.908638596534729</v>
+        <v>0.9086384773254395</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8949402570724487</v>
+        <v>0.8949397802352905</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8362822532653809</v>
+        <v>0.8362821340560913</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8869379758834839</v>
+        <v>0.8869377970695496</v>
       </c>
       <c r="L15" t="n">
         <v>0.9161235094070435</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9241669178009033</v>
+        <v>0.9241664409637451</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8864870071411133</v>
+        <v>0.8864867687225342</v>
       </c>
       <c r="O15" t="n">
-        <v>1.000000238418579</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9104539155960083</v>
+        <v>0.910453736782074</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8529775142669678</v>
+        <v>0.8529771566390991</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8333733081817627</v>
+        <v>0.8333732485771179</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8957282304763794</v>
+        <v>0.895727813243866</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8940631151199341</v>
+        <v>0.894062876701355</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9011842012405396</v>
+        <v>0.9011846780776978</v>
       </c>
       <c r="V15" t="n">
-        <v>0.883326530456543</v>
+        <v>0.8833266496658325</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9150640964508057</v>
+        <v>0.9150638580322266</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8991782665252686</v>
+        <v>0.8991779088973999</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9066460132598877</v>
+        <v>0.9066461324691772</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.9023823738098145</v>
+        <v>0.902381956577301</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.8968706130981445</v>
+        <v>0.896870493888855</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8355642557144165</v>
+        <v>0.8355640769004822</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.8956929445266724</v>
+        <v>0.8956927061080933</v>
       </c>
     </row>
     <row r="16">
@@ -1851,88 +1851,88 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9101829528808594</v>
+        <v>0.9101825952529907</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8673862218856812</v>
+        <v>0.8673859834671021</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8733971118927002</v>
+        <v>0.8733967542648315</v>
       </c>
       <c r="E16" t="n">
-        <v>0.893433153629303</v>
+        <v>0.8934330344200134</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8930953741073608</v>
+        <v>0.893095076084137</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8969775438308716</v>
+        <v>0.8969773054122925</v>
       </c>
       <c r="H16" t="n">
         <v>0.8885284662246704</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8861508369445801</v>
+        <v>0.8861502408981323</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8321028351783752</v>
+        <v>0.8321027755737305</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9071863889694214</v>
+        <v>0.9071865081787109</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9211479425430298</v>
+        <v>0.9211475849151611</v>
       </c>
       <c r="M16" t="n">
-        <v>0.915088951587677</v>
+        <v>0.9150885343551636</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8959065675735474</v>
+        <v>0.8959063291549683</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9104539155960083</v>
+        <v>0.910453736782074</v>
       </c>
       <c r="P16" t="n">
-        <v>1.000000476837158</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.847346305847168</v>
+        <v>0.8473459482192993</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8235707879066467</v>
+        <v>0.8235704898834229</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8813589215278625</v>
+        <v>0.8813591003417969</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9019486308097839</v>
+        <v>0.9019483923912048</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8909293413162231</v>
+        <v>0.8909292221069336</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8984862565994263</v>
+        <v>0.8984858989715576</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9150462746620178</v>
+        <v>0.9150458574295044</v>
       </c>
       <c r="X16" t="n">
         <v>0.8876562118530273</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9192123413085938</v>
+        <v>0.9192124605178833</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8921593427658081</v>
+        <v>0.8921589255332947</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.8949098587036133</v>
+        <v>0.8949093818664551</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8217706680297852</v>
+        <v>0.8217703700065613</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9206446409225464</v>
+        <v>0.9206445217132568</v>
       </c>
     </row>
     <row r="17">
@@ -1945,85 +1945,85 @@
         <v>0.8336291313171387</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8335090279579163</v>
+        <v>0.833509087562561</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8369334936141968</v>
+        <v>0.836932897567749</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8382150530815125</v>
+        <v>0.8382149934768677</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8307888507843018</v>
+        <v>0.8307887315750122</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8332059383392334</v>
+        <v>0.8332055807113647</v>
       </c>
       <c r="H17" t="n">
         <v>0.8626000881195068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8431073427200317</v>
+        <v>0.843107283115387</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9398021697998047</v>
+        <v>0.9398022890090942</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8479938507080078</v>
+        <v>0.8479936718940735</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8533174991607666</v>
+        <v>0.8533173799514771</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8506760597229004</v>
+        <v>0.8506755828857422</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8447829484939575</v>
+        <v>0.844782829284668</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8529775142669678</v>
+        <v>0.8529771566390991</v>
       </c>
       <c r="P17" t="n">
-        <v>0.847346305847168</v>
+        <v>0.8473459482192993</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9999997615814209</v>
+        <v>1.000000357627869</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9344090223312378</v>
+        <v>0.9344087839126587</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8416507244110107</v>
+        <v>0.8416505455970764</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8364711999893188</v>
+        <v>0.836470901966095</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8427741527557373</v>
+        <v>0.8427739143371582</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8257176876068115</v>
+        <v>0.825717031955719</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8499367833137512</v>
+        <v>0.849936842918396</v>
       </c>
       <c r="X17" t="n">
-        <v>0.8467764854431152</v>
+        <v>0.8467761874198914</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8399659395217896</v>
+        <v>0.8399657607078552</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.8588438034057617</v>
+        <v>0.8588434457778931</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8345358371734619</v>
+        <v>0.8345355987548828</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8854494094848633</v>
+        <v>0.8854491710662842</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8531848192214966</v>
+        <v>0.8531845808029175</v>
       </c>
     </row>
     <row r="18">
@@ -2033,88 +2033,88 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8343381881713867</v>
+        <v>0.8343378305435181</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8175127506256104</v>
+        <v>0.8175126314163208</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8352609276771545</v>
+        <v>0.835260808467865</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8337386846542358</v>
+        <v>0.8337384462356567</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8262513875961304</v>
+        <v>0.8262505531311035</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8429336547851562</v>
+        <v>0.8429340124130249</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8523857593536377</v>
+        <v>0.8523854613304138</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8250465393066406</v>
+        <v>0.8250464200973511</v>
       </c>
       <c r="J18" t="n">
         <v>0.9279340505599976</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8295843601226807</v>
+        <v>0.8295843005180359</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8354157209396362</v>
+        <v>0.8354154825210571</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8384671211242676</v>
+        <v>0.8384667634963989</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8360897898674011</v>
+        <v>0.8360894918441772</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8333733081817627</v>
+        <v>0.8333732485771179</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8235707879066467</v>
+        <v>0.8235704898834229</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9344090223312378</v>
+        <v>0.9344087839126587</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9999998807907104</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8214161396026611</v>
+        <v>0.821415901184082</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8266108632087708</v>
+        <v>0.8266110420227051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8321260213851929</v>
+        <v>0.8321259617805481</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7994647622108459</v>
+        <v>0.7994645237922668</v>
       </c>
       <c r="W18" t="n">
-        <v>0.828365683555603</v>
+        <v>0.8283653855323792</v>
       </c>
       <c r="X18" t="n">
-        <v>0.8305207490921021</v>
+        <v>0.8305205106735229</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8186362981796265</v>
+        <v>0.8186360597610474</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.824305534362793</v>
+        <v>0.8243051767349243</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8239538073539734</v>
+        <v>0.8239536285400391</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.897186279296875</v>
+        <v>0.8971858024597168</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8272530436515808</v>
+        <v>0.8272529244422913</v>
       </c>
     </row>
     <row r="19">
@@ -2124,85 +2124,85 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8883686065673828</v>
+        <v>0.8883687257766724</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8419703245162964</v>
+        <v>0.8419700860977173</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8449867963790894</v>
+        <v>0.8449864387512207</v>
       </c>
       <c r="E19" t="n">
         <v>0.8785125017166138</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8723194599151611</v>
+        <v>0.8723193407058716</v>
       </c>
       <c r="G19" t="n">
         <v>0.8932348489761353</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8663286566734314</v>
+        <v>0.8663284778594971</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9006692171096802</v>
+        <v>0.900668740272522</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8274298906326294</v>
+        <v>0.8274297714233398</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8710378408432007</v>
+        <v>0.8710376024246216</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8914902806282043</v>
+        <v>0.8914898633956909</v>
       </c>
       <c r="M19" t="n">
-        <v>0.903888463973999</v>
+        <v>0.9038882851600647</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8714480400085449</v>
+        <v>0.8714476823806763</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8957282304763794</v>
+        <v>0.895727813243866</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8813589215278625</v>
+        <v>0.8813591003417969</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8416507244110107</v>
+        <v>0.8416505455970764</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214161396026611</v>
+        <v>0.821415901184082</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9999999403953552</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8915920257568359</v>
+        <v>0.8915915489196777</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9023893475532532</v>
+        <v>0.9023891687393188</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8749428987503052</v>
+        <v>0.874942421913147</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8950690031051636</v>
+        <v>0.8950689435005188</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8799763917922974</v>
+        <v>0.8799764513969421</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.8868472576141357</v>
+        <v>0.8868473172187805</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.9093791246414185</v>
+        <v>0.9093788862228394</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.8760640621185303</v>
+        <v>0.8760637044906616</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8358195424079895</v>
+        <v>0.8358194828033447</v>
       </c>
       <c r="AC19" t="n">
         <v>0.8798643350601196</v>
@@ -2215,88 +2215,88 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9235917329788208</v>
+        <v>0.9235914945602417</v>
       </c>
       <c r="C20" t="n">
-        <v>0.849434494972229</v>
+        <v>0.8494346141815186</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8615514039993286</v>
+        <v>0.8615512847900391</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9174599647521973</v>
+        <v>0.917460024356842</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8920542001724243</v>
+        <v>0.8920536637306213</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9090330600738525</v>
+        <v>0.9090328812599182</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8732837438583374</v>
+        <v>0.8732834458351135</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8911222219467163</v>
+        <v>0.8911218047142029</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8336665034294128</v>
+        <v>0.8336663246154785</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9023727178573608</v>
+        <v>0.9023722410202026</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9103498458862305</v>
+        <v>0.9103497862815857</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8981676697731018</v>
+        <v>0.8981672525405884</v>
       </c>
       <c r="N20" t="n">
-        <v>0.886219322681427</v>
+        <v>0.8862186670303345</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8940631151199341</v>
+        <v>0.894062876701355</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9019486308097839</v>
+        <v>0.9019483923912048</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8364711999893188</v>
+        <v>0.836470901966095</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8266108632087708</v>
+        <v>0.8266110420227051</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8915920257568359</v>
+        <v>0.8915915489196777</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9999997615814209</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8907653093338013</v>
+        <v>0.8907648324966431</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8683456182479858</v>
+        <v>0.8683454990386963</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9276247620582581</v>
+        <v>0.9276250600814819</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8842158317565918</v>
+        <v>0.8842157125473022</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.8886278867721558</v>
+        <v>0.8886277675628662</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.8980714082717896</v>
+        <v>0.8980710506439209</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8677718639373779</v>
+        <v>0.8677712678909302</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8305901885032654</v>
+        <v>0.8305901288986206</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8808428049087524</v>
+        <v>0.8808424472808838</v>
       </c>
     </row>
     <row r="21">
@@ -2306,88 +2306,88 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8883249163627625</v>
+        <v>0.8883245587348938</v>
       </c>
       <c r="C21" t="n">
-        <v>0.852882981300354</v>
+        <v>0.8528826236724854</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8583704233169556</v>
+        <v>0.858370304107666</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8848069906234741</v>
+        <v>0.8848065733909607</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8831583261489868</v>
+        <v>0.8831580877304077</v>
       </c>
       <c r="G21" t="n">
         <v>0.9008340835571289</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8703348636627197</v>
+        <v>0.8703346252441406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9054946899414062</v>
+        <v>0.9054938554763794</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8291482925415039</v>
+        <v>0.8291481733322144</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8823256492614746</v>
+        <v>0.8823255300521851</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9135844111442566</v>
+        <v>0.9135845899581909</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9168130159378052</v>
+        <v>0.9168126583099365</v>
       </c>
       <c r="N21" t="n">
-        <v>0.882748007774353</v>
+        <v>0.8827479481697083</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9011842012405396</v>
+        <v>0.9011846780776978</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8909293413162231</v>
+        <v>0.8909292221069336</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8427741527557373</v>
+        <v>0.8427739143371582</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8321260213851929</v>
+        <v>0.8321259617805481</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9023893475532532</v>
+        <v>0.9023891687393188</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8907653093338013</v>
+        <v>0.8907648324966431</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9999998211860657</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8583604097366333</v>
+        <v>0.8583604693412781</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9062308073043823</v>
+        <v>0.9062305688858032</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8727902173995972</v>
+        <v>0.8727903366088867</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.8853163719177246</v>
+        <v>0.885316014289856</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.9058578014373779</v>
+        <v>0.9058576822280884</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.9010766744613647</v>
+        <v>0.9010763168334961</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8331699967384338</v>
+        <v>0.83316969871521</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.8845592737197876</v>
+        <v>0.8845596313476562</v>
       </c>
     </row>
     <row r="22">
@@ -2397,88 +2397,88 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8823716640472412</v>
+        <v>0.8823714256286621</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8303762078285217</v>
+        <v>0.8303756713867188</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8407629728317261</v>
+        <v>0.8407632112503052</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8593936562538147</v>
+        <v>0.8593931794166565</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8482007384300232</v>
+        <v>0.8482003808021545</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8653336763381958</v>
+        <v>0.8653331995010376</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8698242902755737</v>
+        <v>0.8698241710662842</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8542855381965637</v>
+        <v>0.8542848825454712</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8119673728942871</v>
+        <v>0.8119672536849976</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8778689503669739</v>
+        <v>0.87786865234375</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8813762068748474</v>
+        <v>0.8813762664794922</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8776522874832153</v>
+        <v>0.8776520490646362</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8582971096038818</v>
+        <v>0.8582968711853027</v>
       </c>
       <c r="O22" t="n">
-        <v>0.883326530456543</v>
+        <v>0.8833266496658325</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8984862565994263</v>
+        <v>0.8984858989715576</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8257176876068115</v>
+        <v>0.825717031955719</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7994647622108459</v>
+        <v>0.7994645237922668</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8749428987503052</v>
+        <v>0.874942421913147</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8683456182479858</v>
+        <v>0.8683454990386963</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8583604097366333</v>
+        <v>0.8583604693412781</v>
       </c>
       <c r="V22" t="n">
-        <v>1.00000011920929</v>
+        <v>1.000000357627869</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8874898552894592</v>
+        <v>0.8874895572662354</v>
       </c>
       <c r="X22" t="n">
-        <v>0.8852674961090088</v>
+        <v>0.8852671384811401</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.9022369980812073</v>
+        <v>0.9022367596626282</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.8617401719093323</v>
+        <v>0.8617396950721741</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.8580697774887085</v>
+        <v>0.8580695390701294</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8172383308410645</v>
+        <v>0.8172379732131958</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.9014617800712585</v>
+        <v>0.9014618396759033</v>
       </c>
     </row>
     <row r="23">
@@ -2488,88 +2488,88 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9374822974205017</v>
+        <v>0.9374818801879883</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8576647043228149</v>
+        <v>0.8576644659042358</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8699272274971008</v>
+        <v>0.869926929473877</v>
       </c>
       <c r="E23" t="n">
-        <v>0.916956901550293</v>
+        <v>0.9169570207595825</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9117148518562317</v>
+        <v>0.911715030670166</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9174145460128784</v>
+        <v>0.9174143671989441</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8939296007156372</v>
+        <v>0.8939295411109924</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9036498665809631</v>
+        <v>0.9036496877670288</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8405823707580566</v>
+        <v>0.8405822515487671</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9212817549705505</v>
+        <v>0.9212815165519714</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9336406588554382</v>
+        <v>0.9336405992507935</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9148710370063782</v>
+        <v>0.9148703813552856</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8976263999938965</v>
+        <v>0.8976262807846069</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9150640964508057</v>
+        <v>0.9150638580322266</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9150462746620178</v>
+        <v>0.9150458574295044</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.8499367833137512</v>
+        <v>0.849936842918396</v>
       </c>
       <c r="R23" t="n">
-        <v>0.828365683555603</v>
+        <v>0.8283653855323792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8950690031051636</v>
+        <v>0.8950689435005188</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9276247620582581</v>
+        <v>0.9276250600814819</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9062308073043823</v>
+        <v>0.9062305688858032</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8874898552894592</v>
+        <v>0.8874895572662354</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.8961538076400757</v>
+        <v>0.8961541652679443</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.9051117897033691</v>
+        <v>0.9051122665405273</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.9058386087417603</v>
+        <v>0.9058381319046021</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.8993154168128967</v>
+        <v>0.8993151187896729</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.8257131576538086</v>
+        <v>0.8257126808166504</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.9100641012191772</v>
+        <v>0.9100639820098877</v>
       </c>
     </row>
     <row r="24">
@@ -2579,88 +2579,88 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8960747122764587</v>
+        <v>0.8960744142532349</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8387265801429749</v>
+        <v>0.8387263417243958</v>
       </c>
       <c r="D24" t="n">
         <v>0.8437125682830811</v>
       </c>
       <c r="E24" t="n">
-        <v>0.887496292591095</v>
+        <v>0.8874961733818054</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8778378963470459</v>
+        <v>0.8778374195098877</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8955031633377075</v>
+        <v>0.8955028057098389</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9046574831008911</v>
+        <v>0.9046571850776672</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8795552849769592</v>
+        <v>0.8795550465583801</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8251742124557495</v>
+        <v>0.8251737356185913</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9014301300048828</v>
+        <v>0.9014304876327515</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9012442827224731</v>
+        <v>0.9012448191642761</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8846296072006226</v>
+        <v>0.8846292495727539</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8827852010726929</v>
+        <v>0.8827848434448242</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8991782665252686</v>
+        <v>0.8991779088973999</v>
       </c>
       <c r="P24" t="n">
         <v>0.8876562118530273</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8467764854431152</v>
+        <v>0.8467761874198914</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8305207490921021</v>
+        <v>0.8305205106735229</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8799763917922974</v>
+        <v>0.8799764513969421</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8842158317565918</v>
+        <v>0.8842157125473022</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8727902173995972</v>
+        <v>0.8727903366088867</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8852674961090088</v>
+        <v>0.8852671384811401</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8961538076400757</v>
+        <v>0.8961541652679443</v>
       </c>
       <c r="X24" t="n">
-        <v>0.9999999403953552</v>
+        <v>0.9999997615814209</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.8765764236450195</v>
+        <v>0.87657630443573</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.8843064308166504</v>
+        <v>0.8843065500259399</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8600653409957886</v>
+        <v>0.8600650429725647</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.829736590385437</v>
+        <v>0.8297363519668579</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.8958688378334045</v>
+        <v>0.8958688974380493</v>
       </c>
     </row>
     <row r="25">
@@ -2670,88 +2670,88 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8949880599975586</v>
+        <v>0.8949875831604004</v>
       </c>
       <c r="C25" t="n">
         <v>0.849388599395752</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8563985824584961</v>
+        <v>0.8563982248306274</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8836581707000732</v>
+        <v>0.8836584091186523</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8872561454772949</v>
+        <v>0.8872556090354919</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8974261283874512</v>
+        <v>0.8974260687828064</v>
       </c>
       <c r="H25" t="n">
-        <v>0.879912257194519</v>
+        <v>0.8799123764038086</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8782399892807007</v>
+        <v>0.878239631652832</v>
       </c>
       <c r="J25" t="n">
-        <v>0.827221155166626</v>
+        <v>0.8272209167480469</v>
       </c>
       <c r="K25" t="n">
         <v>0.9006924629211426</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9059131145477295</v>
+        <v>0.9059126973152161</v>
       </c>
       <c r="M25" t="n">
         <v>0.9190843105316162</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8751000165939331</v>
+        <v>0.8750998973846436</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9066460132598877</v>
+        <v>0.9066461324691772</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9192123413085938</v>
+        <v>0.9192124605178833</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8399659395217896</v>
+        <v>0.8399657607078552</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8186362981796265</v>
+        <v>0.8186360597610474</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8868472576141357</v>
+        <v>0.8868473172187805</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8886278867721558</v>
+        <v>0.8886277675628662</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8853163719177246</v>
+        <v>0.885316014289856</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9022369980812073</v>
+        <v>0.9022367596626282</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9051117897033691</v>
+        <v>0.9051122665405273</v>
       </c>
       <c r="X25" t="n">
-        <v>0.8765764236450195</v>
+        <v>0.87657630443573</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.9999998211860657</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.8873841762542725</v>
+        <v>0.8873839378356934</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.8847143054008484</v>
+        <v>0.8847143650054932</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.8345935344696045</v>
+        <v>0.8345931768417358</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.902002215385437</v>
+        <v>0.9020017385482788</v>
       </c>
     </row>
     <row r="26">
@@ -2761,88 +2761,88 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.902890682220459</v>
+        <v>0.9028902053833008</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8651005029678345</v>
+        <v>0.8651002049446106</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8508414030075073</v>
+        <v>0.850841224193573</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8884457349777222</v>
+        <v>0.8884453773498535</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8881779313087463</v>
+        <v>0.8881773948669434</v>
       </c>
       <c r="G26" t="n">
-        <v>0.901455283164978</v>
+        <v>0.9014550447463989</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8807768225669861</v>
+        <v>0.8807762861251831</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9112921357154846</v>
+        <v>0.9112923145294189</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8362271785736084</v>
+        <v>0.8362268209457397</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8756319880485535</v>
+        <v>0.8756316900253296</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9170732498168945</v>
+        <v>0.9170726537704468</v>
       </c>
       <c r="M26" t="n">
         <v>0.8958896398544312</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9021697044372559</v>
+        <v>0.9021689891815186</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9023823738098145</v>
+        <v>0.902381956577301</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8921593427658081</v>
+        <v>0.8921589255332947</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8588438034057617</v>
+        <v>0.8588434457778931</v>
       </c>
       <c r="R26" t="n">
-        <v>0.824305534362793</v>
+        <v>0.8243051767349243</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9093791246414185</v>
+        <v>0.9093788862228394</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8980714082717896</v>
+        <v>0.8980710506439209</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9058578014373779</v>
+        <v>0.9058576822280884</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8617401719093323</v>
+        <v>0.8617396950721741</v>
       </c>
       <c r="W26" t="n">
-        <v>0.9058386087417603</v>
+        <v>0.9058381319046021</v>
       </c>
       <c r="X26" t="n">
-        <v>0.8843064308166504</v>
+        <v>0.8843065500259399</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.8873841762542725</v>
+        <v>0.8873839378356934</v>
       </c>
       <c r="Z26" t="n">
-        <v>1</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.8854634761810303</v>
+        <v>0.8854629993438721</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8346238136291504</v>
+        <v>0.8346235752105713</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.8862978219985962</v>
+        <v>0.8862972259521484</v>
       </c>
     </row>
     <row r="27">
@@ -2852,88 +2852,88 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8865189552307129</v>
+        <v>0.8865185976028442</v>
       </c>
       <c r="C27" t="n">
-        <v>0.869402289390564</v>
+        <v>0.8694019317626953</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8713870048522949</v>
+        <v>0.8713867664337158</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8731697797775269</v>
+        <v>0.8731695413589478</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8854338526725769</v>
+        <v>0.8854333162307739</v>
       </c>
       <c r="G27" t="n">
         <v>0.8972249031066895</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8693918585777283</v>
+        <v>0.8693917989730835</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8981694579124451</v>
+        <v>0.8981688618659973</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8342908024787903</v>
+        <v>0.8342905044555664</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8725012540817261</v>
+        <v>0.8725007772445679</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9002515077590942</v>
+        <v>0.9002512693405151</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9150595664978027</v>
+        <v>0.9150591492652893</v>
       </c>
       <c r="N27" t="n">
-        <v>0.882618248462677</v>
+        <v>0.8826179504394531</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8968706130981445</v>
+        <v>0.896870493888855</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8949098587036133</v>
+        <v>0.8949093818664551</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8345358371734619</v>
+        <v>0.8345355987548828</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8239538073539734</v>
+        <v>0.8239536285400391</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8760640621185303</v>
+        <v>0.8760637044906616</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8677718639373779</v>
+        <v>0.8677712678909302</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9010766744613647</v>
+        <v>0.9010763168334961</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8580697774887085</v>
+        <v>0.8580695390701294</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8993154168128967</v>
+        <v>0.8993151187896729</v>
       </c>
       <c r="X27" t="n">
-        <v>0.8600653409957886</v>
+        <v>0.8600650429725647</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.8847143054008484</v>
+        <v>0.8847143650054932</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.8854634761810303</v>
+        <v>0.8854629993438721</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.000000357627869</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.8222634196281433</v>
+        <v>0.822263240814209</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8883249759674072</v>
+        <v>0.8883247375488281</v>
       </c>
     </row>
     <row r="28">
@@ -2943,88 +2943,88 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8228821754455566</v>
+        <v>0.8228815793991089</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8341293931007385</v>
+        <v>0.8341289758682251</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8330405950546265</v>
+        <v>0.8330402970314026</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8222305178642273</v>
+        <v>0.8222304582595825</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8245714902877808</v>
+        <v>0.8245711326599121</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8328536748886108</v>
+        <v>0.8328535556793213</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8496972322463989</v>
+        <v>0.8496968746185303</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8332096338272095</v>
+        <v>0.8332093954086304</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8821119070053101</v>
+        <v>0.8821115493774414</v>
       </c>
       <c r="K28" t="n">
-        <v>0.817221999168396</v>
+        <v>0.8172218799591064</v>
       </c>
       <c r="L28" t="n">
-        <v>0.833482027053833</v>
+        <v>0.8334816098213196</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8425793051719666</v>
+        <v>0.8425792455673218</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8427293300628662</v>
+        <v>0.842729389667511</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8355642557144165</v>
+        <v>0.8355640769004822</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8217706680297852</v>
+        <v>0.8217703700065613</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8854494094848633</v>
+        <v>0.8854491710662842</v>
       </c>
       <c r="R28" t="n">
-        <v>0.897186279296875</v>
+        <v>0.8971858024597168</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8358195424079895</v>
+        <v>0.8358194828033447</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8305901885032654</v>
+        <v>0.8305901288986206</v>
       </c>
       <c r="U28" t="n">
-        <v>0.8331699967384338</v>
+        <v>0.83316969871521</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8172383308410645</v>
+        <v>0.8172379732131958</v>
       </c>
       <c r="W28" t="n">
-        <v>0.8257131576538086</v>
+        <v>0.8257126808166504</v>
       </c>
       <c r="X28" t="n">
-        <v>0.829736590385437</v>
+        <v>0.8297363519668579</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.8345935344696045</v>
+        <v>0.8345931768417358</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.8346238136291504</v>
+        <v>0.8346235752105713</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.8222634196281433</v>
+        <v>0.822263240814209</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.00000011920929</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.8268973827362061</v>
+        <v>0.8268972635269165</v>
       </c>
     </row>
     <row r="29">
@@ -3034,85 +3034,85 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9079517722129822</v>
+        <v>0.9079517126083374</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8390929102897644</v>
+        <v>0.8390926122665405</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8458732962608337</v>
+        <v>0.8458731174468994</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8859279155731201</v>
+        <v>0.8859280347824097</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8842787742614746</v>
+        <v>0.8842782974243164</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8862299919128418</v>
+        <v>0.8862297534942627</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8852790594100952</v>
+        <v>0.8852788209915161</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8896946907043457</v>
+        <v>0.8896943330764771</v>
       </c>
       <c r="J29" t="n">
         <v>0.8334486484527588</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8965610265731812</v>
+        <v>0.8965604901313782</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9069328904151917</v>
+        <v>0.9069327116012573</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9070229530334473</v>
+        <v>0.9070228338241577</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8750876188278198</v>
+        <v>0.8750870227813721</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8956929445266724</v>
+        <v>0.8956927061080933</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9206446409225464</v>
+        <v>0.9206445217132568</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8531848192214966</v>
+        <v>0.8531845808029175</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8272530436515808</v>
+        <v>0.8272529244422913</v>
       </c>
       <c r="S29" t="n">
         <v>0.8798643350601196</v>
       </c>
       <c r="T29" t="n">
-        <v>0.8808428049087524</v>
+        <v>0.8808424472808838</v>
       </c>
       <c r="U29" t="n">
-        <v>0.8845592737197876</v>
+        <v>0.8845596313476562</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9014617800712585</v>
+        <v>0.9014618396759033</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9100641012191772</v>
+        <v>0.9100639820098877</v>
       </c>
       <c r="X29" t="n">
-        <v>0.8958688378334045</v>
+        <v>0.8958688974380493</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.902002215385437</v>
+        <v>0.9020017385482788</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.8862978219985962</v>
+        <v>0.8862972259521484</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8883249759674072</v>
+        <v>0.8883247375488281</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.8268973827362061</v>
+        <v>0.8268972635269165</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>

--- a/generated/teacher_teacher_similarity.xlsx
+++ b/generated/teacher_teacher_similarity.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,88 +577,88 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>1.000000357627869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8524665236473083</v>
+        <v>0.8524669408798218</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8686808347702026</v>
+        <v>0.8686813712120056</v>
       </c>
       <c r="E2" t="n">
         <v>0.9127810001373291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9104167222976685</v>
+        <v>0.9104170799255371</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9211148023605347</v>
+        <v>0.9211149215698242</v>
       </c>
       <c r="H2" t="n">
-        <v>0.887531042098999</v>
+        <v>0.8875312805175781</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8951929211616516</v>
+        <v>0.8951934576034546</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8302701711654663</v>
+        <v>0.8338233232498169</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9121061563491821</v>
+        <v>0.9121062755584717</v>
       </c>
       <c r="L2" t="n">
         <v>0.9243653416633606</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9101783633232117</v>
+        <v>0.9101786017417908</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8995309472084045</v>
+        <v>0.899531364440918</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8957883715629578</v>
+        <v>0.8957887887954712</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9101825952529907</v>
+        <v>0.9101829528808594</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8336291313171387</v>
+        <v>0.8557331562042236</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8343378305435181</v>
+        <v>0.9148001670837402</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8883687257766724</v>
+        <v>0.8883686065673828</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9235914945602417</v>
+        <v>0.9235917329788208</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8883245587348938</v>
+        <v>0.8883249163627625</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8823714256286621</v>
+        <v>0.8823716640472412</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9374818801879883</v>
+        <v>0.9374822974205017</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8960744142532349</v>
+        <v>0.8960747122764587</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8949875831604004</v>
+        <v>0.8949880599975586</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9028902053833008</v>
+        <v>0.902890682220459</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8865185976028442</v>
+        <v>0.8865189552307129</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8228815793991089</v>
+        <v>0.8228821754455566</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9079517126083374</v>
+        <v>0.9079517722129822</v>
       </c>
     </row>
     <row r="3">
@@ -668,88 +668,88 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8524665236473083</v>
+        <v>0.8524669408798218</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8664517998695374</v>
+        <v>0.866452157497406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8364719748497009</v>
+        <v>0.8364723920822144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8491683602333069</v>
+        <v>0.8491685390472412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8560551404953003</v>
+        <v>0.8560552597045898</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8405083417892456</v>
+        <v>0.8405088782310486</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8631149530410767</v>
+        <v>0.8631153702735901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8289868235588074</v>
+        <v>0.8355795741081238</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8384640216827393</v>
+        <v>0.8384642601013184</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8597980141639709</v>
+        <v>0.8597980737686157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8446508646011353</v>
+        <v>0.8446515202522278</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8732753992080688</v>
+        <v>0.8732755780220032</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8553775548934937</v>
+        <v>0.8553780317306519</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8673859834671021</v>
+        <v>0.8673862218856812</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.833509087562561</v>
+        <v>0.8494427800178528</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8175126314163208</v>
+        <v>0.8339660167694092</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8419700860977173</v>
+        <v>0.8419703245162964</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8494346141815186</v>
+        <v>0.849434494972229</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8528826236724854</v>
+        <v>0.852882981300354</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8303756713867188</v>
+        <v>0.8303762078285217</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8576644659042358</v>
+        <v>0.8576647043228149</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8387263417243958</v>
+        <v>0.8387265801429749</v>
       </c>
       <c r="Y3" t="n">
         <v>0.849388599395752</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.8651002049446106</v>
+        <v>0.8651005029678345</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8694019317626953</v>
+        <v>0.869402289390564</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8341289758682251</v>
+        <v>0.8341293931007385</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8390926122665405</v>
+        <v>0.8390929102897644</v>
       </c>
     </row>
     <row r="4">
@@ -759,88 +759,88 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8686808347702026</v>
+        <v>0.8686813712120056</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8664517998695374</v>
+        <v>0.866452157497406</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999996423721313</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="E4" t="n">
         <v>0.8476735353469849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8546262383460999</v>
+        <v>0.8546265363693237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.851108193397522</v>
+        <v>0.8511085510253906</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8565832376480103</v>
+        <v>0.8565835952758789</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8535357713699341</v>
+        <v>0.8535363674163818</v>
       </c>
       <c r="J4" t="n">
-        <v>0.834916353225708</v>
+        <v>0.8385263681411743</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8530595302581787</v>
+        <v>0.8530595898628235</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8679360151290894</v>
+        <v>0.8679365515708923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8521713018417358</v>
+        <v>0.8521715402603149</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8850942254066467</v>
+        <v>0.8850944638252258</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8547220230102539</v>
+        <v>0.8547224402427673</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8733967542648315</v>
+        <v>0.8733971118927002</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.836932897567749</v>
+        <v>0.8564963936805725</v>
       </c>
       <c r="R4" t="n">
-        <v>0.835260808467865</v>
+        <v>0.8605788946151733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8449864387512207</v>
+        <v>0.8449867963790894</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8615512847900391</v>
+        <v>0.8615514039993286</v>
       </c>
       <c r="U4" t="n">
-        <v>0.858370304107666</v>
+        <v>0.8583704233169556</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8407632112503052</v>
+        <v>0.8407629728317261</v>
       </c>
       <c r="W4" t="n">
-        <v>0.869926929473877</v>
+        <v>0.8699272274971008</v>
       </c>
       <c r="X4" t="n">
         <v>0.8437125682830811</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8563982248306274</v>
+        <v>0.8563985824584961</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.850841224193573</v>
+        <v>0.8508414030075073</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.8713867664337158</v>
+        <v>0.8713870048522949</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8330402970314026</v>
+        <v>0.8330405950546265</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8458731174468994</v>
+        <v>0.8458732962608337</v>
       </c>
     </row>
     <row r="5">
@@ -853,85 +853,85 @@
         <v>0.9127810001373291</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8364719748497009</v>
+        <v>0.8364723920822144</v>
       </c>
       <c r="D5" t="n">
         <v>0.8476735353469849</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8988657593727112</v>
+        <v>0.8988659381866455</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9047037363052368</v>
+        <v>0.9047038555145264</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8700432777404785</v>
+        <v>0.8700436353683472</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8900554776191711</v>
+        <v>0.8900558352470398</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8357341289520264</v>
+        <v>0.8352994918823242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9087117910385132</v>
+        <v>0.908711850643158</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9142200946807861</v>
+        <v>0.9142202734947205</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8921324014663696</v>
+        <v>0.8921328783035278</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8772101402282715</v>
+        <v>0.8772107362747192</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8865792751312256</v>
+        <v>0.8865797519683838</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8934330344200134</v>
+        <v>0.893433153629303</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8382149934768677</v>
+        <v>0.8678715229034424</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8337384462356567</v>
+        <v>0.9103295207023621</v>
       </c>
       <c r="S5" t="n">
         <v>0.8785125017166138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.917460024356842</v>
+        <v>0.9174599647521973</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8848065733909607</v>
+        <v>0.8848069906234741</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8593931794166565</v>
+        <v>0.8593936562538147</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9169570207595825</v>
+        <v>0.916956901550293</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8874961733818054</v>
+        <v>0.887496292591095</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8836584091186523</v>
+        <v>0.8836581707000732</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8884453773498535</v>
+        <v>0.8884457349777222</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8731695413589478</v>
+        <v>0.8731697797775269</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8222304582595825</v>
+        <v>0.8222305178642273</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8859280347824097</v>
+        <v>0.8859279155731201</v>
       </c>
     </row>
     <row r="6">
@@ -941,88 +941,88 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9104167222976685</v>
+        <v>0.9104170799255371</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8491683602333069</v>
+        <v>0.8491685390472412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8546262383460999</v>
+        <v>0.8546265363693237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8988657593727112</v>
+        <v>0.8988659381866455</v>
       </c>
       <c r="F6" t="n">
-        <v>1.00000011920929</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9213026762008667</v>
+        <v>0.9213030338287354</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8774891495704651</v>
+        <v>0.8774892091751099</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8921391367912292</v>
+        <v>0.8921396732330322</v>
       </c>
       <c r="J6" t="n">
-        <v>0.834198534488678</v>
+        <v>0.8328001499176025</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8980823755264282</v>
+        <v>0.8980830311775208</v>
       </c>
       <c r="L6" t="n">
         <v>0.9284849166870117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8996173739433289</v>
+        <v>0.8996177911758423</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8997945785522461</v>
+        <v>0.8997952938079834</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8863773345947266</v>
+        <v>0.8863776922225952</v>
       </c>
       <c r="P6" t="n">
-        <v>0.893095076084137</v>
+        <v>0.8930953741073608</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8307887315750122</v>
+        <v>0.8595305681228638</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8262505531311035</v>
+        <v>0.8917438387870789</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8723193407058716</v>
+        <v>0.8723194599151611</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8920536637306213</v>
+        <v>0.8920542001724243</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8831580877304077</v>
+        <v>0.8831583261489868</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8482003808021545</v>
+        <v>0.8482007384300232</v>
       </c>
       <c r="W6" t="n">
-        <v>0.911715030670166</v>
+        <v>0.9117148518562317</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8778374195098877</v>
+        <v>0.8778378963470459</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8872556090354919</v>
+        <v>0.8872561454772949</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8881773948669434</v>
+        <v>0.8881779313087463</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8854333162307739</v>
+        <v>0.8854338526725769</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8245711326599121</v>
+        <v>0.8245714902877808</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8842782974243164</v>
+        <v>0.8842787742614746</v>
       </c>
     </row>
     <row r="7">
@@ -1032,88 +1032,88 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9211148023605347</v>
+        <v>0.9211149215698242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8560551404953003</v>
+        <v>0.8560552597045898</v>
       </c>
       <c r="D7" t="n">
-        <v>0.851108193397522</v>
+        <v>0.8511085510253906</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9047037363052368</v>
+        <v>0.9047038555145264</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9213026762008667</v>
+        <v>0.9213030338287354</v>
       </c>
       <c r="G7" t="n">
-        <v>1.000000238418579</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8846269845962524</v>
+        <v>0.8846272230148315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9021722078323364</v>
+        <v>0.9021725654602051</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8370207548141479</v>
+        <v>0.8361713290214539</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9011682271957397</v>
+        <v>0.9011684060096741</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9326137900352478</v>
+        <v>0.9326138496398926</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9128487110137939</v>
+        <v>0.912848949432373</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8978871703147888</v>
+        <v>0.8978878259658813</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9132239818572998</v>
+        <v>0.913224458694458</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8969773054122925</v>
+        <v>0.8969775438308716</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8332055807113647</v>
+        <v>0.8597217798233032</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8429340124130249</v>
+        <v>0.9027513861656189</v>
       </c>
       <c r="S7" t="n">
         <v>0.8932348489761353</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9090328812599182</v>
+        <v>0.9090330600738525</v>
       </c>
       <c r="U7" t="n">
         <v>0.9008340835571289</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8653331995010376</v>
+        <v>0.8653336763381958</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9174143671989441</v>
+        <v>0.9174145460128784</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8955028057098389</v>
+        <v>0.8955031633377075</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8974260687828064</v>
+        <v>0.8974261283874512</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9014550447463989</v>
+        <v>0.901455283164978</v>
       </c>
       <c r="AA7" t="n">
         <v>0.8972249031066895</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8328535556793213</v>
+        <v>0.8328536748886108</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8862297534942627</v>
+        <v>0.8862299919128418</v>
       </c>
     </row>
     <row r="8">
@@ -1123,88 +1123,88 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.887531042098999</v>
+        <v>0.8875312805175781</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8405083417892456</v>
+        <v>0.8405088782310486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8565832376480103</v>
+        <v>0.8565835952758789</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8700432777404785</v>
+        <v>0.8700436353683472</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8774891495704651</v>
+        <v>0.8774892091751099</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8846269845962524</v>
+        <v>0.8846272230148315</v>
       </c>
       <c r="H8" t="n">
-        <v>1.000000238418579</v>
+        <v>0.9999999403953552</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8745768070220947</v>
+        <v>0.8745768666267395</v>
       </c>
       <c r="J8" t="n">
-        <v>0.844151496887207</v>
+        <v>0.8501796722412109</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8788841366767883</v>
+        <v>0.8788844347000122</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8941789865493774</v>
+        <v>0.8941791653633118</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8847023248672485</v>
+        <v>0.884702742099762</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8881731033325195</v>
+        <v>0.8881736397743225</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9086384773254395</v>
+        <v>0.908638596534729</v>
       </c>
       <c r="P8" t="n">
         <v>0.8885284662246704</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8626000881195068</v>
+        <v>0.8680731058120728</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8523854613304138</v>
+        <v>0.8672974705696106</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8663284778594971</v>
+        <v>0.8663286566734314</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8732834458351135</v>
+        <v>0.8732837438583374</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8703346252441406</v>
+        <v>0.8703348636627197</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8698241710662842</v>
+        <v>0.8698242902755737</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8939295411109924</v>
+        <v>0.8939296007156372</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9046571850776672</v>
+        <v>0.9046574831008911</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8799123764038086</v>
+        <v>0.879912257194519</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8807762861251831</v>
+        <v>0.8807768225669861</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8693917989730835</v>
+        <v>0.8693918585777283</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8496968746185303</v>
+        <v>0.8496972322463989</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.8852788209915161</v>
+        <v>0.8852790594100952</v>
       </c>
     </row>
     <row r="9">
@@ -1214,179 +1214,179 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8951929211616516</v>
+        <v>0.8951934576034546</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8631149530410767</v>
+        <v>0.8631153702735901</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8535357713699341</v>
+        <v>0.8535363674163818</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8900554776191711</v>
+        <v>0.8900558352470398</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8921391367912292</v>
+        <v>0.8921396732330322</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9021722078323364</v>
+        <v>0.9021725654602051</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8745768070220947</v>
+        <v>0.8745768666267395</v>
       </c>
       <c r="I9" t="n">
         <v>0.9999998807907104</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8434652090072632</v>
+        <v>0.8474165797233582</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8714591860771179</v>
+        <v>0.8714597821235657</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8997251987457275</v>
+        <v>0.8997255563735962</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9117178916931152</v>
+        <v>0.9117185473442078</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8979407548904419</v>
+        <v>0.8979413509368896</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8949397802352905</v>
+        <v>0.8949402570724487</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8861502408981323</v>
+        <v>0.8861508369445801</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.843107283115387</v>
+        <v>0.872855544090271</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8250464200973511</v>
+        <v>0.8784716725349426</v>
       </c>
       <c r="S9" t="n">
-        <v>0.900668740272522</v>
+        <v>0.9006692171096802</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8911218047142029</v>
+        <v>0.8911222219467163</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9054938554763794</v>
+        <v>0.9054946899414062</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8542848825454712</v>
+        <v>0.8542855381965637</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9036496877670288</v>
+        <v>0.9036498665809631</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8795550465583801</v>
+        <v>0.8795552849769592</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.878239631652832</v>
+        <v>0.8782399892807007</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9112923145294189</v>
+        <v>0.9112921357154846</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8981688618659973</v>
+        <v>0.8981694579124451</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8332093954086304</v>
+        <v>0.8332096338272095</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8896943330764771</v>
+        <v>0.8896946907043457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8302701711654663</v>
+        <v>0.8338233232498169</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8289868235588074</v>
+        <v>0.8355795741081238</v>
       </c>
       <c r="D10" t="n">
-        <v>0.834916353225708</v>
+        <v>0.8385263681411743</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8357341289520264</v>
+        <v>0.8352994918823242</v>
       </c>
       <c r="F10" t="n">
-        <v>0.834198534488678</v>
+        <v>0.8328001499176025</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8370207548141479</v>
+        <v>0.8361713290214539</v>
       </c>
       <c r="H10" t="n">
-        <v>0.844151496887207</v>
+        <v>0.8501796722412109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8434652090072632</v>
+        <v>0.8474165797233582</v>
       </c>
       <c r="J10" t="n">
-        <v>1.000000357627869</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="K10" t="n">
-        <v>0.830353856086731</v>
+        <v>0.8403846025466919</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8460994362831116</v>
+        <v>0.8464421033859253</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8435173034667969</v>
+        <v>0.8473173379898071</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8366098999977112</v>
+        <v>0.840134859085083</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8362821340560913</v>
+        <v>0.8455361127853394</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8321027755737305</v>
+        <v>0.839849591255188</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9398022890090942</v>
+        <v>0.8559294939041138</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9279340505599976</v>
+        <v>0.8472533226013184</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8274297714233398</v>
+        <v>0.8322204947471619</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8336663246154785</v>
+        <v>0.8391239643096924</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8291481733322144</v>
+        <v>0.8325496912002563</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8119672536849976</v>
+        <v>0.8171987533569336</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8405822515487671</v>
+        <v>0.8453735113143921</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8251737356185913</v>
+        <v>0.8302240967750549</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8272209167480469</v>
+        <v>0.8405318260192871</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8362268209457397</v>
+        <v>0.8465471267700195</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8342905044555664</v>
+        <v>0.8375923633575439</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8821115493774414</v>
+        <v>0.8891992568969727</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8334486484527588</v>
+        <v>0.8408675193786621</v>
       </c>
     </row>
     <row r="11">
@@ -1396,88 +1396,88 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9121061563491821</v>
+        <v>0.9121062755584717</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8384640216827393</v>
+        <v>0.8384642601013184</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8530595302581787</v>
+        <v>0.8530595898628235</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9087117910385132</v>
+        <v>0.908711850643158</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8980823755264282</v>
+        <v>0.8980830311775208</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9011682271957397</v>
+        <v>0.9011684060096741</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8788841366767883</v>
+        <v>0.8788844347000122</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8714591860771179</v>
+        <v>0.8714597821235657</v>
       </c>
       <c r="J11" t="n">
-        <v>0.830353856086731</v>
+        <v>0.8403846025466919</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9053002595901489</v>
+        <v>0.905300498008728</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8927915096282959</v>
+        <v>0.8927918672561646</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8723717927932739</v>
+        <v>0.8723720908164978</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8869377970695496</v>
+        <v>0.8869379758834839</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9071865081787109</v>
+        <v>0.9071863889694214</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8479936718940735</v>
+        <v>0.8738576173782349</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8295843005180359</v>
+        <v>0.8863324522972107</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8710376024246216</v>
+        <v>0.8710378408432007</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9023722410202026</v>
+        <v>0.9023727178573608</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8823255300521851</v>
+        <v>0.8823256492614746</v>
       </c>
       <c r="V11" t="n">
-        <v>0.87786865234375</v>
+        <v>0.8778689503669739</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9212815165519714</v>
+        <v>0.9212817549705505</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9014304876327515</v>
+        <v>0.9014301300048828</v>
       </c>
       <c r="Y11" t="n">
         <v>0.9006924629211426</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8756316900253296</v>
+        <v>0.8756319880485535</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.8725007772445679</v>
+        <v>0.8725012540817261</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8172218799591064</v>
+        <v>0.817221999168396</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8965604901313782</v>
+        <v>0.8965610265731812</v>
       </c>
     </row>
     <row r="12">
@@ -1490,85 +1490,85 @@
         <v>0.9243653416633606</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8597980141639709</v>
+        <v>0.8597980737686157</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8679360151290894</v>
+        <v>0.8679365515708923</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9142200946807861</v>
+        <v>0.9142202734947205</v>
       </c>
       <c r="F12" t="n">
         <v>0.9284849166870117</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9326137900352478</v>
+        <v>0.9326138496398926</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8941789865493774</v>
+        <v>0.8941791653633118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8997251987457275</v>
+        <v>0.8997255563735962</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8460994362831116</v>
+        <v>0.8464421033859253</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9053002595901489</v>
+        <v>0.905300498008728</v>
       </c>
       <c r="L12" t="n">
-        <v>1.000000357627869</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9193594455718994</v>
+        <v>0.9193600416183472</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9056235551834106</v>
+        <v>0.9056236743927002</v>
       </c>
       <c r="O12" t="n">
         <v>0.9161235094070435</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9211475849151611</v>
+        <v>0.9211479425430298</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8533173799514771</v>
+        <v>0.8683022856712341</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8354154825210571</v>
+        <v>0.9069734811782837</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8914898633956909</v>
+        <v>0.8914902806282043</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9103497862815857</v>
+        <v>0.9103498458862305</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9135845899581909</v>
+        <v>0.9135844111442566</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8813762664794922</v>
+        <v>0.8813762068748474</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9336405992507935</v>
+        <v>0.9336406588554382</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9012448191642761</v>
+        <v>0.9012442827224731</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.9059126973152161</v>
+        <v>0.9059131145477295</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.9170726537704468</v>
+        <v>0.9170732498168945</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.9002512693405151</v>
+        <v>0.9002515077590942</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8334816098213196</v>
+        <v>0.833482027053833</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.9069327116012573</v>
+        <v>0.9069328904151917</v>
       </c>
     </row>
     <row r="13">
@@ -1578,73 +1578,73 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9101783633232117</v>
+        <v>0.9101786017417908</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8446508646011353</v>
+        <v>0.8446515202522278</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8521713018417358</v>
+        <v>0.8521715402603149</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8921324014663696</v>
+        <v>0.8921328783035278</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8996173739433289</v>
+        <v>0.8996177911758423</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9128487110137939</v>
+        <v>0.912848949432373</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8847023248672485</v>
+        <v>0.884702742099762</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9117178916931152</v>
+        <v>0.9117185473442078</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8435173034667969</v>
+        <v>0.8473173379898071</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8927915096282959</v>
+        <v>0.8927918672561646</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9193594455718994</v>
+        <v>0.9193600416183472</v>
       </c>
       <c r="M13" t="n">
-        <v>1.000000238418579</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8829382061958313</v>
+        <v>0.8829388618469238</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9241664409637451</v>
+        <v>0.9241669178009033</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9150885343551636</v>
+        <v>0.915088951587677</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8506755828857422</v>
+        <v>0.8703169822692871</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8384667634963989</v>
+        <v>0.8780305981636047</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9038882851600647</v>
+        <v>0.903888463973999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8981672525405884</v>
+        <v>0.8981676697731018</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9168126583099365</v>
+        <v>0.9168130159378052</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8776520490646362</v>
+        <v>0.8776522874832153</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9148703813552856</v>
+        <v>0.9148710370063782</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8846292495727539</v>
+        <v>0.8846296072006226</v>
       </c>
       <c r="Y13" t="n">
         <v>0.9190843105316162</v>
@@ -1653,13 +1653,13 @@
         <v>0.8958896398544312</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9150591492652893</v>
+        <v>0.9150595664978027</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8425792455673218</v>
+        <v>0.8425793051719666</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.9070228338241577</v>
+        <v>0.9070229530334473</v>
       </c>
     </row>
     <row r="14">
@@ -1669,88 +1669,88 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8995309472084045</v>
+        <v>0.899531364440918</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8732753992080688</v>
+        <v>0.8732755780220032</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8850942254066467</v>
+        <v>0.8850944638252258</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8772101402282715</v>
+        <v>0.8772107362747192</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8997945785522461</v>
+        <v>0.8997952938079834</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8978871703147888</v>
+        <v>0.8978878259658813</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8881731033325195</v>
+        <v>0.8881736397743225</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8979407548904419</v>
+        <v>0.8979413509368896</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8366098999977112</v>
+        <v>0.840134859085083</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8723717927932739</v>
+        <v>0.8723720908164978</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9056235551834106</v>
+        <v>0.9056236743927002</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8829382061958313</v>
+        <v>0.8829388618469238</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8864867687225342</v>
+        <v>0.8864870071411133</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8959063291549683</v>
+        <v>0.8959065675735474</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.844782829284668</v>
+        <v>0.8756363391876221</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8360894918441772</v>
+        <v>0.8884810209274292</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8714476823806763</v>
+        <v>0.8714480400085449</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8862186670303345</v>
+        <v>0.886219322681427</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8827479481697083</v>
+        <v>0.882748007774353</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8582968711853027</v>
+        <v>0.8582971096038818</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8976262807846069</v>
+        <v>0.8976263999938965</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8827848434448242</v>
+        <v>0.8827852010726929</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8750998973846436</v>
+        <v>0.8751000165939331</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.9021689891815186</v>
+        <v>0.9021697044372559</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8826179504394531</v>
+        <v>0.882618248462677</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.842729389667511</v>
+        <v>0.8427293300628662</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.8750870227813721</v>
+        <v>0.8750876188278198</v>
       </c>
     </row>
     <row r="15">
@@ -1760,88 +1760,88 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8957883715629578</v>
+        <v>0.8957887887954712</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8553775548934937</v>
+        <v>0.8553780317306519</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8547220230102539</v>
+        <v>0.8547224402427673</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8865792751312256</v>
+        <v>0.8865797519683838</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8863773345947266</v>
+        <v>0.8863776922225952</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9132239818572998</v>
+        <v>0.913224458694458</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9086384773254395</v>
+        <v>0.908638596534729</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8949397802352905</v>
+        <v>0.8949402570724487</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8362821340560913</v>
+        <v>0.8455361127853394</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8869377970695496</v>
+        <v>0.8869379758834839</v>
       </c>
       <c r="L15" t="n">
         <v>0.9161235094070435</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9241664409637451</v>
+        <v>0.9241669178009033</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8864867687225342</v>
+        <v>0.8864870071411133</v>
       </c>
       <c r="O15" t="n">
-        <v>1.00000011920929</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="P15" t="n">
-        <v>0.910453736782074</v>
+        <v>0.9104539155960083</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8529771566390991</v>
+        <v>0.8715478181838989</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8333732485771179</v>
+        <v>0.8753183484077454</v>
       </c>
       <c r="S15" t="n">
-        <v>0.895727813243866</v>
+        <v>0.8957282304763794</v>
       </c>
       <c r="T15" t="n">
-        <v>0.894062876701355</v>
+        <v>0.8940631151199341</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9011846780776978</v>
+        <v>0.9011842012405396</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8833266496658325</v>
+        <v>0.883326530456543</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9150638580322266</v>
+        <v>0.9150640964508057</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8991779088973999</v>
+        <v>0.8991782665252686</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9066461324691772</v>
+        <v>0.9066460132598877</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.902381956577301</v>
+        <v>0.9023823738098145</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.896870493888855</v>
+        <v>0.8968706130981445</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8355640769004822</v>
+        <v>0.8355642557144165</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.8956927061080933</v>
+        <v>0.8956929445266724</v>
       </c>
     </row>
     <row r="16">
@@ -1851,270 +1851,270 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9101825952529907</v>
+        <v>0.9101829528808594</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8673859834671021</v>
+        <v>0.8673862218856812</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8733967542648315</v>
+        <v>0.8733971118927002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8934330344200134</v>
+        <v>0.893433153629303</v>
       </c>
       <c r="F16" t="n">
-        <v>0.893095076084137</v>
+        <v>0.8930953741073608</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8969773054122925</v>
+        <v>0.8969775438308716</v>
       </c>
       <c r="H16" t="n">
         <v>0.8885284662246704</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8861502408981323</v>
+        <v>0.8861508369445801</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8321027755737305</v>
+        <v>0.839849591255188</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9071865081787109</v>
+        <v>0.9071863889694214</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9211475849151611</v>
+        <v>0.9211479425430298</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9150885343551636</v>
+        <v>0.915088951587677</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8959063291549683</v>
+        <v>0.8959065675735474</v>
       </c>
       <c r="O16" t="n">
-        <v>0.910453736782074</v>
+        <v>0.9104539155960083</v>
       </c>
       <c r="P16" t="n">
-        <v>1.00000011920929</v>
+        <v>1.000000476837158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8473459482192993</v>
+        <v>0.8749116659164429</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8235704898834229</v>
+        <v>0.8724351525306702</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8813591003417969</v>
+        <v>0.8813589215278625</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9019483923912048</v>
+        <v>0.9019486308097839</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8909292221069336</v>
+        <v>0.8909293413162231</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8984858989715576</v>
+        <v>0.8984862565994263</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9150458574295044</v>
+        <v>0.9150462746620178</v>
       </c>
       <c r="X16" t="n">
         <v>0.8876562118530273</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9192124605178833</v>
+        <v>0.9192123413085938</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8921589255332947</v>
+        <v>0.8921593427658081</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.8949093818664551</v>
+        <v>0.8949098587036133</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8217703700065613</v>
+        <v>0.8217706680297852</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9206445217132568</v>
+        <v>0.9206446409225464</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8336291313171387</v>
+        <v>0.8557331562042236</v>
       </c>
       <c r="C17" t="n">
-        <v>0.833509087562561</v>
+        <v>0.8494427800178528</v>
       </c>
       <c r="D17" t="n">
-        <v>0.836932897567749</v>
+        <v>0.8564963936805725</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8382149934768677</v>
+        <v>0.8678715229034424</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8307887315750122</v>
+        <v>0.8595305681228638</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8332055807113647</v>
+        <v>0.8597217798233032</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8626000881195068</v>
+        <v>0.8680731058120728</v>
       </c>
       <c r="I17" t="n">
-        <v>0.843107283115387</v>
+        <v>0.872855544090271</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9398022890090942</v>
+        <v>0.8559294939041138</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8479936718940735</v>
+        <v>0.8738576173782349</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8533173799514771</v>
+        <v>0.8683022856712341</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8506755828857422</v>
+        <v>0.8703169822692871</v>
       </c>
       <c r="N17" t="n">
-        <v>0.844782829284668</v>
+        <v>0.8756363391876221</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8529771566390991</v>
+        <v>0.8715478181838989</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8473459482192993</v>
+        <v>0.8749116659164429</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.000000357627869</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9344087839126587</v>
+        <v>0.8680868148803711</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8416505455970764</v>
+        <v>0.8592532873153687</v>
       </c>
       <c r="T17" t="n">
-        <v>0.836470901966095</v>
+        <v>0.8667904734611511</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8427739143371582</v>
+        <v>0.88332200050354</v>
       </c>
       <c r="V17" t="n">
-        <v>0.825717031955719</v>
+        <v>0.8306186199188232</v>
       </c>
       <c r="W17" t="n">
-        <v>0.849936842918396</v>
+        <v>0.8835150003433228</v>
       </c>
       <c r="X17" t="n">
-        <v>0.8467761874198914</v>
+        <v>0.8595641255378723</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8399657607078552</v>
+        <v>0.8608036637306213</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.8588434457778931</v>
+        <v>0.8739874362945557</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8345355987548828</v>
+        <v>0.8623703718185425</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8854491710662842</v>
+        <v>0.8068119287490845</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8531845808029175</v>
+        <v>0.8646461963653564</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8343378305435181</v>
+        <v>0.9148001670837402</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8175126314163208</v>
+        <v>0.8339660167694092</v>
       </c>
       <c r="D18" t="n">
-        <v>0.835260808467865</v>
+        <v>0.8605788946151733</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8337384462356567</v>
+        <v>0.9103295207023621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8262505531311035</v>
+        <v>0.8917438387870789</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8429340124130249</v>
+        <v>0.9027513861656189</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8523854613304138</v>
+        <v>0.8672974705696106</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8250464200973511</v>
+        <v>0.8784716725349426</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9279340505599976</v>
+        <v>0.8472533226013184</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8295843005180359</v>
+        <v>0.8863324522972107</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8354154825210571</v>
+        <v>0.9069734811782837</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8384667634963989</v>
+        <v>0.8780305981636047</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8360894918441772</v>
+        <v>0.8884810209274292</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8333732485771179</v>
+        <v>0.8753183484077454</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8235704898834229</v>
+        <v>0.8724351525306702</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9344087839126587</v>
+        <v>0.8680868148803711</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.821415901184082</v>
+        <v>0.87009197473526</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8266110420227051</v>
+        <v>0.9034159183502197</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8321259617805481</v>
+        <v>0.8811439275741577</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7994645237922668</v>
+        <v>0.8455395102500916</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8283653855323792</v>
+        <v>0.9069024324417114</v>
       </c>
       <c r="X18" t="n">
-        <v>0.8305205106735229</v>
+        <v>0.8810880184173584</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8186360597610474</v>
+        <v>0.8645888566970825</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.8243051767349243</v>
+        <v>0.8926560878753662</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8239536285400391</v>
+        <v>0.8618605136871338</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8971858024597168</v>
+        <v>0.8211671113967896</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8272529244422913</v>
+        <v>0.8684271574020386</v>
       </c>
     </row>
     <row r="19">
@@ -2124,85 +2124,85 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8883687257766724</v>
+        <v>0.8883686065673828</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8419700860977173</v>
+        <v>0.8419703245162964</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8449864387512207</v>
+        <v>0.8449867963790894</v>
       </c>
       <c r="E19" t="n">
         <v>0.8785125017166138</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8723193407058716</v>
+        <v>0.8723194599151611</v>
       </c>
       <c r="G19" t="n">
         <v>0.8932348489761353</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8663284778594971</v>
+        <v>0.8663286566734314</v>
       </c>
       <c r="I19" t="n">
-        <v>0.900668740272522</v>
+        <v>0.9006692171096802</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8274297714233398</v>
+        <v>0.8322204947471619</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8710376024246216</v>
+        <v>0.8710378408432007</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8914898633956909</v>
+        <v>0.8914902806282043</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9038882851600647</v>
+        <v>0.903888463973999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8714476823806763</v>
+        <v>0.8714480400085449</v>
       </c>
       <c r="O19" t="n">
-        <v>0.895727813243866</v>
+        <v>0.8957282304763794</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8813591003417969</v>
+        <v>0.8813589215278625</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8416505455970764</v>
+        <v>0.8592532873153687</v>
       </c>
       <c r="R19" t="n">
-        <v>0.821415901184082</v>
+        <v>0.87009197473526</v>
       </c>
       <c r="S19" t="n">
-        <v>1.000000238418579</v>
+        <v>0.9999999403953552</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8915915489196777</v>
+        <v>0.8915920257568359</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9023891687393188</v>
+        <v>0.9023893475532532</v>
       </c>
       <c r="V19" t="n">
-        <v>0.874942421913147</v>
+        <v>0.8749428987503052</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8950689435005188</v>
+        <v>0.8950690031051636</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8799764513969421</v>
+        <v>0.8799763917922974</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.8868473172187805</v>
+        <v>0.8868472576141357</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.9093788862228394</v>
+        <v>0.9093791246414185</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.8760637044906616</v>
+        <v>0.8760640621185303</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8358194828033447</v>
+        <v>0.8358195424079895</v>
       </c>
       <c r="AC19" t="n">
         <v>0.8798643350601196</v>
@@ -2215,88 +2215,88 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9235914945602417</v>
+        <v>0.9235917329788208</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8494346141815186</v>
+        <v>0.849434494972229</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8615512847900391</v>
+        <v>0.8615514039993286</v>
       </c>
       <c r="E20" t="n">
-        <v>0.917460024356842</v>
+        <v>0.9174599647521973</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8920536637306213</v>
+        <v>0.8920542001724243</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9090328812599182</v>
+        <v>0.9090330600738525</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8732834458351135</v>
+        <v>0.8732837438583374</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8911218047142029</v>
+        <v>0.8911222219467163</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8336663246154785</v>
+        <v>0.8391239643096924</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9023722410202026</v>
+        <v>0.9023727178573608</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9103497862815857</v>
+        <v>0.9103498458862305</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8981672525405884</v>
+        <v>0.8981676697731018</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8862186670303345</v>
+        <v>0.886219322681427</v>
       </c>
       <c r="O20" t="n">
-        <v>0.894062876701355</v>
+        <v>0.8940631151199341</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9019483923912048</v>
+        <v>0.9019486308097839</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.836470901966095</v>
+        <v>0.8667904734611511</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8266110420227051</v>
+        <v>0.9034159183502197</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8915915489196777</v>
+        <v>0.8915920257568359</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9999997615814209</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8907648324966431</v>
+        <v>0.8907653093338013</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8683454990386963</v>
+        <v>0.8683456182479858</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9276250600814819</v>
+        <v>0.9276247620582581</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8842157125473022</v>
+        <v>0.8842158317565918</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.8886277675628662</v>
+        <v>0.8886278867721558</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.8980710506439209</v>
+        <v>0.8980714082717896</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8677712678909302</v>
+        <v>0.8677718639373779</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8305901288986206</v>
+        <v>0.8305901885032654</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8808424472808838</v>
+        <v>0.8808428049087524</v>
       </c>
     </row>
     <row r="21">
@@ -2306,88 +2306,88 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8883245587348938</v>
+        <v>0.8883249163627625</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8528826236724854</v>
+        <v>0.852882981300354</v>
       </c>
       <c r="D21" t="n">
-        <v>0.858370304107666</v>
+        <v>0.8583704233169556</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8848065733909607</v>
+        <v>0.8848069906234741</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8831580877304077</v>
+        <v>0.8831583261489868</v>
       </c>
       <c r="G21" t="n">
         <v>0.9008340835571289</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8703346252441406</v>
+        <v>0.8703348636627197</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9054938554763794</v>
+        <v>0.9054946899414062</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8291481733322144</v>
+        <v>0.8325496912002563</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8823255300521851</v>
+        <v>0.8823256492614746</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9135845899581909</v>
+        <v>0.9135844111442566</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9168126583099365</v>
+        <v>0.9168130159378052</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8827479481697083</v>
+        <v>0.882748007774353</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9011846780776978</v>
+        <v>0.9011842012405396</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8909292221069336</v>
+        <v>0.8909293413162231</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8427739143371582</v>
+        <v>0.88332200050354</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8321259617805481</v>
+        <v>0.8811439275741577</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9023891687393188</v>
+        <v>0.9023893475532532</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8907648324966431</v>
+        <v>0.8907653093338013</v>
       </c>
       <c r="U21" t="n">
-        <v>1.00000011920929</v>
+        <v>0.9999998211860657</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8583604693412781</v>
+        <v>0.8583604097366333</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9062305688858032</v>
+        <v>0.9062308073043823</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8727903366088867</v>
+        <v>0.8727902173995972</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.885316014289856</v>
+        <v>0.8853163719177246</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.9058576822280884</v>
+        <v>0.9058578014373779</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.9010763168334961</v>
+        <v>0.9010766744613647</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.83316969871521</v>
+        <v>0.8331699967384338</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.8845596313476562</v>
+        <v>0.8845592737197876</v>
       </c>
     </row>
     <row r="22">
@@ -2397,88 +2397,88 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8823714256286621</v>
+        <v>0.8823716640472412</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8303756713867188</v>
+        <v>0.8303762078285217</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8407632112503052</v>
+        <v>0.8407629728317261</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8593931794166565</v>
+        <v>0.8593936562538147</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8482003808021545</v>
+        <v>0.8482007384300232</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8653331995010376</v>
+        <v>0.8653336763381958</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8698241710662842</v>
+        <v>0.8698242902755737</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8542848825454712</v>
+        <v>0.8542855381965637</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8119672536849976</v>
+        <v>0.8171987533569336</v>
       </c>
       <c r="K22" t="n">
-        <v>0.87786865234375</v>
+        <v>0.8778689503669739</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8813762664794922</v>
+        <v>0.8813762068748474</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8776520490646362</v>
+        <v>0.8776522874832153</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8582968711853027</v>
+        <v>0.8582971096038818</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8833266496658325</v>
+        <v>0.883326530456543</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8984858989715576</v>
+        <v>0.8984862565994263</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.825717031955719</v>
+        <v>0.8306186199188232</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7994645237922668</v>
+        <v>0.8455395102500916</v>
       </c>
       <c r="S22" t="n">
-        <v>0.874942421913147</v>
+        <v>0.8749428987503052</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8683454990386963</v>
+        <v>0.8683456182479858</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8583604693412781</v>
+        <v>0.8583604097366333</v>
       </c>
       <c r="V22" t="n">
-        <v>1.000000357627869</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8874895572662354</v>
+        <v>0.8874898552894592</v>
       </c>
       <c r="X22" t="n">
-        <v>0.8852671384811401</v>
+        <v>0.8852674961090088</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.9022367596626282</v>
+        <v>0.9022369980812073</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.8617396950721741</v>
+        <v>0.8617401719093323</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.8580695390701294</v>
+        <v>0.8580697774887085</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8172379732131958</v>
+        <v>0.8172383308410645</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.9014618396759033</v>
+        <v>0.9014617800712585</v>
       </c>
     </row>
     <row r="23">
@@ -2488,88 +2488,88 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9374818801879883</v>
+        <v>0.9374822974205017</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8576644659042358</v>
+        <v>0.8576647043228149</v>
       </c>
       <c r="D23" t="n">
-        <v>0.869926929473877</v>
+        <v>0.8699272274971008</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9169570207595825</v>
+        <v>0.916956901550293</v>
       </c>
       <c r="F23" t="n">
-        <v>0.911715030670166</v>
+        <v>0.9117148518562317</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9174143671989441</v>
+        <v>0.9174145460128784</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8939295411109924</v>
+        <v>0.8939296007156372</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9036496877670288</v>
+        <v>0.9036498665809631</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8405822515487671</v>
+        <v>0.8453735113143921</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9212815165519714</v>
+        <v>0.9212817549705505</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9336405992507935</v>
+        <v>0.9336406588554382</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9148703813552856</v>
+        <v>0.9148710370063782</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8976262807846069</v>
+        <v>0.8976263999938965</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9150638580322266</v>
+        <v>0.9150640964508057</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9150458574295044</v>
+        <v>0.9150462746620178</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.849936842918396</v>
+        <v>0.8835150003433228</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8283653855323792</v>
+        <v>0.9069024324417114</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8950689435005188</v>
+        <v>0.8950690031051636</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9276250600814819</v>
+        <v>0.9276247620582581</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9062305688858032</v>
+        <v>0.9062308073043823</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8874895572662354</v>
+        <v>0.8874898552894592</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.8961541652679443</v>
+        <v>0.8961538076400757</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.9051122665405273</v>
+        <v>0.9051117897033691</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.9058381319046021</v>
+        <v>0.9058386087417603</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.8993151187896729</v>
+        <v>0.8993154168128967</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.8257126808166504</v>
+        <v>0.8257131576538086</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.9100639820098877</v>
+        <v>0.9100641012191772</v>
       </c>
     </row>
     <row r="24">
@@ -2579,88 +2579,88 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8960744142532349</v>
+        <v>0.8960747122764587</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8387263417243958</v>
+        <v>0.8387265801429749</v>
       </c>
       <c r="D24" t="n">
         <v>0.8437125682830811</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8874961733818054</v>
+        <v>0.887496292591095</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8778374195098877</v>
+        <v>0.8778378963470459</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8955028057098389</v>
+        <v>0.8955031633377075</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9046571850776672</v>
+        <v>0.9046574831008911</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8795550465583801</v>
+        <v>0.8795552849769592</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8251737356185913</v>
+        <v>0.8302240967750549</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9014304876327515</v>
+        <v>0.9014301300048828</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9012448191642761</v>
+        <v>0.9012442827224731</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8846292495727539</v>
+        <v>0.8846296072006226</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8827848434448242</v>
+        <v>0.8827852010726929</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8991779088973999</v>
+        <v>0.8991782665252686</v>
       </c>
       <c r="P24" t="n">
         <v>0.8876562118530273</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8467761874198914</v>
+        <v>0.8595641255378723</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8305205106735229</v>
+        <v>0.8810880184173584</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8799764513969421</v>
+        <v>0.8799763917922974</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8842157125473022</v>
+        <v>0.8842158317565918</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8727903366088867</v>
+        <v>0.8727902173995972</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8852671384811401</v>
+        <v>0.8852674961090088</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8961541652679443</v>
+        <v>0.8961538076400757</v>
       </c>
       <c r="X24" t="n">
-        <v>0.9999997615814209</v>
+        <v>0.9999999403953552</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.87657630443573</v>
+        <v>0.8765764236450195</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.8843065500259399</v>
+        <v>0.8843064308166504</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8600650429725647</v>
+        <v>0.8600653409957886</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.8297363519668579</v>
+        <v>0.829736590385437</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.8958688974380493</v>
+        <v>0.8958688378334045</v>
       </c>
     </row>
     <row r="25">
@@ -2670,88 +2670,88 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8949875831604004</v>
+        <v>0.8949880599975586</v>
       </c>
       <c r="C25" t="n">
         <v>0.849388599395752</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8563982248306274</v>
+        <v>0.8563985824584961</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8836584091186523</v>
+        <v>0.8836581707000732</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8872556090354919</v>
+        <v>0.8872561454772949</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8974260687828064</v>
+        <v>0.8974261283874512</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8799123764038086</v>
+        <v>0.879912257194519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.878239631652832</v>
+        <v>0.8782399892807007</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8272209167480469</v>
+        <v>0.8405318260192871</v>
       </c>
       <c r="K25" t="n">
         <v>0.9006924629211426</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9059126973152161</v>
+        <v>0.9059131145477295</v>
       </c>
       <c r="M25" t="n">
         <v>0.9190843105316162</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8750998973846436</v>
+        <v>0.8751000165939331</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9066461324691772</v>
+        <v>0.9066460132598877</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9192124605178833</v>
+        <v>0.9192123413085938</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8399657607078552</v>
+        <v>0.8608036637306213</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8186360597610474</v>
+        <v>0.8645888566970825</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8868473172187805</v>
+        <v>0.8868472576141357</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8886277675628662</v>
+        <v>0.8886278867721558</v>
       </c>
       <c r="U25" t="n">
-        <v>0.885316014289856</v>
+        <v>0.8853163719177246</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9022367596626282</v>
+        <v>0.9022369980812073</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9051122665405273</v>
+        <v>0.9051117897033691</v>
       </c>
       <c r="X25" t="n">
-        <v>0.87657630443573</v>
+        <v>0.8765764236450195</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.00000011920929</v>
+        <v>0.9999998211860657</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.8873839378356934</v>
+        <v>0.8873841762542725</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.8847143650054932</v>
+        <v>0.8847143054008484</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.8345931768417358</v>
+        <v>0.8345935344696045</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.9020017385482788</v>
+        <v>0.902002215385437</v>
       </c>
     </row>
     <row r="26">
@@ -2761,88 +2761,88 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9028902053833008</v>
+        <v>0.902890682220459</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8651002049446106</v>
+        <v>0.8651005029678345</v>
       </c>
       <c r="D26" t="n">
-        <v>0.850841224193573</v>
+        <v>0.8508414030075073</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8884453773498535</v>
+        <v>0.8884457349777222</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8881773948669434</v>
+        <v>0.8881779313087463</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9014550447463989</v>
+        <v>0.901455283164978</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8807762861251831</v>
+        <v>0.8807768225669861</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9112923145294189</v>
+        <v>0.9112921357154846</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8362268209457397</v>
+        <v>0.8465471267700195</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8756316900253296</v>
+        <v>0.8756319880485535</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9170726537704468</v>
+        <v>0.9170732498168945</v>
       </c>
       <c r="M26" t="n">
         <v>0.8958896398544312</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9021689891815186</v>
+        <v>0.9021697044372559</v>
       </c>
       <c r="O26" t="n">
-        <v>0.902381956577301</v>
+        <v>0.9023823738098145</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8921589255332947</v>
+        <v>0.8921593427658081</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8588434457778931</v>
+        <v>0.8739874362945557</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8243051767349243</v>
+        <v>0.8926560878753662</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9093788862228394</v>
+        <v>0.9093791246414185</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8980710506439209</v>
+        <v>0.8980714082717896</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9058576822280884</v>
+        <v>0.9058578014373779</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8617396950721741</v>
+        <v>0.8617401719093323</v>
       </c>
       <c r="W26" t="n">
-        <v>0.9058381319046021</v>
+        <v>0.9058386087417603</v>
       </c>
       <c r="X26" t="n">
-        <v>0.8843065500259399</v>
+        <v>0.8843064308166504</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.8873839378356934</v>
+        <v>0.8873841762542725</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.9999998807907104</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.8854629993438721</v>
+        <v>0.8854634761810303</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8346235752105713</v>
+        <v>0.8346238136291504</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.8862972259521484</v>
+        <v>0.8862978219985962</v>
       </c>
     </row>
     <row r="27">
@@ -2852,88 +2852,88 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8865185976028442</v>
+        <v>0.8865189552307129</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8694019317626953</v>
+        <v>0.869402289390564</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8713867664337158</v>
+        <v>0.8713870048522949</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8731695413589478</v>
+        <v>0.8731697797775269</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8854333162307739</v>
+        <v>0.8854338526725769</v>
       </c>
       <c r="G27" t="n">
         <v>0.8972249031066895</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8693917989730835</v>
+        <v>0.8693918585777283</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8981688618659973</v>
+        <v>0.8981694579124451</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8342905044555664</v>
+        <v>0.8375923633575439</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8725007772445679</v>
+        <v>0.8725012540817261</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9002512693405151</v>
+        <v>0.9002515077590942</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9150591492652893</v>
+        <v>0.9150595664978027</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8826179504394531</v>
+        <v>0.882618248462677</v>
       </c>
       <c r="O27" t="n">
-        <v>0.896870493888855</v>
+        <v>0.8968706130981445</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8949093818664551</v>
+        <v>0.8949098587036133</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8345355987548828</v>
+        <v>0.8623703718185425</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8239536285400391</v>
+        <v>0.8618605136871338</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8760637044906616</v>
+        <v>0.8760640621185303</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8677712678909302</v>
+        <v>0.8677718639373779</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9010763168334961</v>
+        <v>0.9010766744613647</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8580695390701294</v>
+        <v>0.8580697774887085</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8993151187896729</v>
+        <v>0.8993154168128967</v>
       </c>
       <c r="X27" t="n">
-        <v>0.8600650429725647</v>
+        <v>0.8600653409957886</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.8847143650054932</v>
+        <v>0.8847143054008484</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.8854629993438721</v>
+        <v>0.8854634761810303</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.000000238418579</v>
+        <v>1.000000357627869</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.822263240814209</v>
+        <v>0.8222634196281433</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8883247375488281</v>
+        <v>0.8883249759674072</v>
       </c>
     </row>
     <row r="28">
@@ -2943,88 +2943,88 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8228815793991089</v>
+        <v>0.8228821754455566</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8341289758682251</v>
+        <v>0.8341293931007385</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8330402970314026</v>
+        <v>0.8330405950546265</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8222304582595825</v>
+        <v>0.8222305178642273</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8245711326599121</v>
+        <v>0.8245714902877808</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8328535556793213</v>
+        <v>0.8328536748886108</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8496968746185303</v>
+        <v>0.8496972322463989</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8332093954086304</v>
+        <v>0.8332096338272095</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8821115493774414</v>
+        <v>0.8891992568969727</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8172218799591064</v>
+        <v>0.817221999168396</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8334816098213196</v>
+        <v>0.833482027053833</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8425792455673218</v>
+        <v>0.8425793051719666</v>
       </c>
       <c r="N28" t="n">
-        <v>0.842729389667511</v>
+        <v>0.8427293300628662</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8355640769004822</v>
+        <v>0.8355642557144165</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8217703700065613</v>
+        <v>0.8217706680297852</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8854491710662842</v>
+        <v>0.8068119287490845</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8971858024597168</v>
+        <v>0.8211671113967896</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8358194828033447</v>
+        <v>0.8358195424079895</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8305901288986206</v>
+        <v>0.8305901885032654</v>
       </c>
       <c r="U28" t="n">
-        <v>0.83316969871521</v>
+        <v>0.8331699967384338</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8172379732131958</v>
+        <v>0.8172383308410645</v>
       </c>
       <c r="W28" t="n">
-        <v>0.8257126808166504</v>
+        <v>0.8257131576538086</v>
       </c>
       <c r="X28" t="n">
-        <v>0.8297363519668579</v>
+        <v>0.829736590385437</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.8345931768417358</v>
+        <v>0.8345935344696045</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.8346235752105713</v>
+        <v>0.8346238136291504</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.822263240814209</v>
+        <v>0.8222634196281433</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.8268972635269165</v>
+        <v>0.8268973827362061</v>
       </c>
     </row>
     <row r="29">
@@ -3034,85 +3034,85 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9079517126083374</v>
+        <v>0.9079517722129822</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8390926122665405</v>
+        <v>0.8390929102897644</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8458731174468994</v>
+        <v>0.8458732962608337</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8859280347824097</v>
+        <v>0.8859279155731201</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8842782974243164</v>
+        <v>0.8842787742614746</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8862297534942627</v>
+        <v>0.8862299919128418</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8852788209915161</v>
+        <v>0.8852790594100952</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8896943330764771</v>
+        <v>0.8896946907043457</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8334486484527588</v>
+        <v>0.8408675193786621</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8965604901313782</v>
+        <v>0.8965610265731812</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9069327116012573</v>
+        <v>0.9069328904151917</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9070228338241577</v>
+        <v>0.9070229530334473</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8750870227813721</v>
+        <v>0.8750876188278198</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8956927061080933</v>
+        <v>0.8956929445266724</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9206445217132568</v>
+        <v>0.9206446409225464</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8531845808029175</v>
+        <v>0.8646461963653564</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8272529244422913</v>
+        <v>0.8684271574020386</v>
       </c>
       <c r="S29" t="n">
         <v>0.8798643350601196</v>
       </c>
       <c r="T29" t="n">
-        <v>0.8808424472808838</v>
+        <v>0.8808428049087524</v>
       </c>
       <c r="U29" t="n">
-        <v>0.8845596313476562</v>
+        <v>0.8845592737197876</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9014618396759033</v>
+        <v>0.9014617800712585</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9100639820098877</v>
+        <v>0.9100641012191772</v>
       </c>
       <c r="X29" t="n">
-        <v>0.8958688974380493</v>
+        <v>0.8958688378334045</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.9020017385482788</v>
+        <v>0.902002215385437</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.8862972259521484</v>
+        <v>0.8862978219985962</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8883247375488281</v>
+        <v>0.8883249759674072</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.8268972635269165</v>
+        <v>0.8268973827362061</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>

--- a/generated/teacher_teacher_similarity.xlsx
+++ b/generated/teacher_teacher_similarity.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>Phung-DucTuan</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>TranLamAnhDuong</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>LiuTianxiang</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -601,7 +601,7 @@
         <v>0.8951934576034546</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8338233232498169</v>
+        <v>0.8302707672119141</v>
       </c>
       <c r="K2" t="n">
         <v>0.9121062755584717</v>
@@ -622,10 +622,10 @@
         <v>0.9101829528808594</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8557331562042236</v>
+        <v>0.8336291313171387</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9148001670837402</v>
+        <v>0.8343381881713867</v>
       </c>
       <c r="S2" t="n">
         <v>0.8883686065673828</v>
@@ -692,7 +692,7 @@
         <v>0.8631153702735901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8355795741081238</v>
+        <v>0.8289872407913208</v>
       </c>
       <c r="K3" t="n">
         <v>0.8384642601013184</v>
@@ -713,10 +713,10 @@
         <v>0.8673862218856812</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8494427800178528</v>
+        <v>0.8335090279579163</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8339660167694092</v>
+        <v>0.8175127506256104</v>
       </c>
       <c r="S3" t="n">
         <v>0.8419703245162964</v>
@@ -783,7 +783,7 @@
         <v>0.8535363674163818</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8385263681411743</v>
+        <v>0.8349167704582214</v>
       </c>
       <c r="K4" t="n">
         <v>0.8530595898628235</v>
@@ -804,10 +804,10 @@
         <v>0.8733971118927002</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8564963936805725</v>
+        <v>0.8369334936141968</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8605788946151733</v>
+        <v>0.8352609276771545</v>
       </c>
       <c r="S4" t="n">
         <v>0.8449867963790894</v>
@@ -874,7 +874,7 @@
         <v>0.8900558352470398</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8352994918823242</v>
+        <v>0.8357346057891846</v>
       </c>
       <c r="K5" t="n">
         <v>0.908711850643158</v>
@@ -895,10 +895,10 @@
         <v>0.893433153629303</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8678715229034424</v>
+        <v>0.8382150530815125</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9103295207023621</v>
+        <v>0.8337386846542358</v>
       </c>
       <c r="S5" t="n">
         <v>0.8785125017166138</v>
@@ -965,7 +965,7 @@
         <v>0.8921396732330322</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8328001499176025</v>
+        <v>0.8341986536979675</v>
       </c>
       <c r="K6" t="n">
         <v>0.8980830311775208</v>
@@ -986,10 +986,10 @@
         <v>0.8930953741073608</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8595305681228638</v>
+        <v>0.8307888507843018</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8917438387870789</v>
+        <v>0.8262513875961304</v>
       </c>
       <c r="S6" t="n">
         <v>0.8723194599151611</v>
@@ -1056,7 +1056,7 @@
         <v>0.9021725654602051</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8361713290214539</v>
+        <v>0.8370206356048584</v>
       </c>
       <c r="K7" t="n">
         <v>0.9011684060096741</v>
@@ -1077,10 +1077,10 @@
         <v>0.8969775438308716</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8597217798233032</v>
+        <v>0.8332059383392334</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9027513861656189</v>
+        <v>0.8429336547851562</v>
       </c>
       <c r="S7" t="n">
         <v>0.8932348489761353</v>
@@ -1147,7 +1147,7 @@
         <v>0.8745768666267395</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8501796722412109</v>
+        <v>0.8441516160964966</v>
       </c>
       <c r="K8" t="n">
         <v>0.8788844347000122</v>
@@ -1168,10 +1168,10 @@
         <v>0.8885284662246704</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8680731058120728</v>
+        <v>0.8626000881195068</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8672974705696106</v>
+        <v>0.8523857593536377</v>
       </c>
       <c r="S8" t="n">
         <v>0.8663286566734314</v>
@@ -1238,7 +1238,7 @@
         <v>0.9999998807907104</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8474165797233582</v>
+        <v>0.8434658050537109</v>
       </c>
       <c r="K9" t="n">
         <v>0.8714597821235657</v>
@@ -1259,10 +1259,10 @@
         <v>0.8861508369445801</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.872855544090271</v>
+        <v>0.8431073427200317</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8784716725349426</v>
+        <v>0.8250465393066406</v>
       </c>
       <c r="S9" t="n">
         <v>0.9006692171096802</v>
@@ -1301,92 +1301,92 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>Phung-DucTuan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8338233232498169</v>
+        <v>0.8302707672119141</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8355795741081238</v>
+        <v>0.8289872407913208</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8385263681411743</v>
+        <v>0.8349167704582214</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8352994918823242</v>
+        <v>0.8357346057891846</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8328001499176025</v>
+        <v>0.8341986536979675</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8361713290214539</v>
+        <v>0.8370206356048584</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8501796722412109</v>
+        <v>0.8441516160964966</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8474165797233582</v>
+        <v>0.8434658050537109</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9999996423721313</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8403846025466919</v>
+        <v>0.8303543329238892</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8464421033859253</v>
+        <v>0.8460994958877563</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8473173379898071</v>
+        <v>0.8435174226760864</v>
       </c>
       <c r="N10" t="n">
-        <v>0.840134859085083</v>
+        <v>0.8366104364395142</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8455361127853394</v>
+        <v>0.8362822532653809</v>
       </c>
       <c r="P10" t="n">
-        <v>0.839849591255188</v>
+        <v>0.8321028351783752</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8559294939041138</v>
+        <v>0.9398021697998047</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8472533226013184</v>
+        <v>0.9279340505599976</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8322204947471619</v>
+        <v>0.8274298906326294</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8391239643096924</v>
+        <v>0.8336665034294128</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8325496912002563</v>
+        <v>0.8291482925415039</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8171987533569336</v>
+        <v>0.8119673728942871</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8453735113143921</v>
+        <v>0.8405823707580566</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8302240967750549</v>
+        <v>0.8251742124557495</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8405318260192871</v>
+        <v>0.827221155166626</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8465471267700195</v>
+        <v>0.8362271785736084</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8375923633575439</v>
+        <v>0.8342908024787903</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8891992568969727</v>
+        <v>0.8821119070053101</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8408675193786621</v>
+        <v>0.8334486484527588</v>
       </c>
     </row>
     <row r="11">
@@ -1420,7 +1420,7 @@
         <v>0.8714597821235657</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8403846025466919</v>
+        <v>0.8303543329238892</v>
       </c>
       <c r="K11" t="n">
         <v>0.9999998807907104</v>
@@ -1441,10 +1441,10 @@
         <v>0.9071863889694214</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8738576173782349</v>
+        <v>0.8479938507080078</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8863324522972107</v>
+        <v>0.8295843601226807</v>
       </c>
       <c r="S11" t="n">
         <v>0.8710378408432007</v>
@@ -1511,7 +1511,7 @@
         <v>0.8997255563735962</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8464421033859253</v>
+        <v>0.8460994958877563</v>
       </c>
       <c r="K12" t="n">
         <v>0.905300498008728</v>
@@ -1532,10 +1532,10 @@
         <v>0.9211479425430298</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8683022856712341</v>
+        <v>0.8533174991607666</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9069734811782837</v>
+        <v>0.8354157209396362</v>
       </c>
       <c r="S12" t="n">
         <v>0.8914902806282043</v>
@@ -1602,7 +1602,7 @@
         <v>0.9117185473442078</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8473173379898071</v>
+        <v>0.8435174226760864</v>
       </c>
       <c r="K13" t="n">
         <v>0.8927918672561646</v>
@@ -1623,10 +1623,10 @@
         <v>0.915088951587677</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8703169822692871</v>
+        <v>0.8506760597229004</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8780305981636047</v>
+        <v>0.8384671211242676</v>
       </c>
       <c r="S13" t="n">
         <v>0.903888463973999</v>
@@ -1693,7 +1693,7 @@
         <v>0.8979413509368896</v>
       </c>
       <c r="J14" t="n">
-        <v>0.840134859085083</v>
+        <v>0.8366104364395142</v>
       </c>
       <c r="K14" t="n">
         <v>0.8723720908164978</v>
@@ -1714,10 +1714,10 @@
         <v>0.8959065675735474</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8756363391876221</v>
+        <v>0.8447829484939575</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8884810209274292</v>
+        <v>0.8360897898674011</v>
       </c>
       <c r="S14" t="n">
         <v>0.8714480400085449</v>
@@ -1784,7 +1784,7 @@
         <v>0.8949402570724487</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8455361127853394</v>
+        <v>0.8362822532653809</v>
       </c>
       <c r="K15" t="n">
         <v>0.8869379758834839</v>
@@ -1805,10 +1805,10 @@
         <v>0.9104539155960083</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8715478181838989</v>
+        <v>0.8529775142669678</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8753183484077454</v>
+        <v>0.8333733081817627</v>
       </c>
       <c r="S15" t="n">
         <v>0.8957282304763794</v>
@@ -1875,7 +1875,7 @@
         <v>0.8861508369445801</v>
       </c>
       <c r="J16" t="n">
-        <v>0.839849591255188</v>
+        <v>0.8321028351783752</v>
       </c>
       <c r="K16" t="n">
         <v>0.9071863889694214</v>
@@ -1896,10 +1896,10 @@
         <v>1.000000476837158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8749116659164429</v>
+        <v>0.847346305847168</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8724351525306702</v>
+        <v>0.8235707879066467</v>
       </c>
       <c r="S16" t="n">
         <v>0.8813589215278625</v>
@@ -1938,183 +1938,183 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>TranLamAnhDuong</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8557331562042236</v>
+        <v>0.8336291313171387</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8494427800178528</v>
+        <v>0.8335090279579163</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8564963936805725</v>
+        <v>0.8369334936141968</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8678715229034424</v>
+        <v>0.8382150530815125</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8595305681228638</v>
+        <v>0.8307888507843018</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8597217798233032</v>
+        <v>0.8332059383392334</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8680731058120728</v>
+        <v>0.8626000881195068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.872855544090271</v>
+        <v>0.8431073427200317</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8559294939041138</v>
+        <v>0.9398021697998047</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8738576173782349</v>
+        <v>0.8479938507080078</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8683022856712341</v>
+        <v>0.8533174991607666</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8703169822692871</v>
+        <v>0.8506760597229004</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8756363391876221</v>
+        <v>0.8447829484939575</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8715478181838989</v>
+        <v>0.8529775142669678</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8749116659164429</v>
+        <v>0.847346305847168</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.000000238418579</v>
+        <v>0.9999997615814209</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8680868148803711</v>
+        <v>0.9344090223312378</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8592532873153687</v>
+        <v>0.8416507244110107</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8667904734611511</v>
+        <v>0.8364711999893188</v>
       </c>
       <c r="U17" t="n">
-        <v>0.88332200050354</v>
+        <v>0.8427741527557373</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8306186199188232</v>
+        <v>0.8257176876068115</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8835150003433228</v>
+        <v>0.8499367833137512</v>
       </c>
       <c r="X17" t="n">
-        <v>0.8595641255378723</v>
+        <v>0.8467764854431152</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8608036637306213</v>
+        <v>0.8399659395217896</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.8739874362945557</v>
+        <v>0.8588438034057617</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8623703718185425</v>
+        <v>0.8345358371734619</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8068119287490845</v>
+        <v>0.8854494094848633</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8646461963653564</v>
+        <v>0.8531848192214966</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>LiuTianxiang</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9148001670837402</v>
+        <v>0.8343381881713867</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8339660167694092</v>
+        <v>0.8175127506256104</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8605788946151733</v>
+        <v>0.8352609276771545</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9103295207023621</v>
+        <v>0.8337386846542358</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8917438387870789</v>
+        <v>0.8262513875961304</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9027513861656189</v>
+        <v>0.8429336547851562</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8672974705696106</v>
+        <v>0.8523857593536377</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8784716725349426</v>
+        <v>0.8250465393066406</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8472533226013184</v>
+        <v>0.9279340505599976</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8863324522972107</v>
+        <v>0.8295843601226807</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9069734811782837</v>
+        <v>0.8354157209396362</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8780305981636047</v>
+        <v>0.8384671211242676</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8884810209274292</v>
+        <v>0.8360897898674011</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8753183484077454</v>
+        <v>0.8333733081817627</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8724351525306702</v>
+        <v>0.8235707879066467</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8680868148803711</v>
+        <v>0.9344090223312378</v>
       </c>
       <c r="R18" t="n">
-        <v>1.000000238418579</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="S18" t="n">
-        <v>0.87009197473526</v>
+        <v>0.8214161396026611</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9034159183502197</v>
+        <v>0.8266108632087708</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8811439275741577</v>
+        <v>0.8321260213851929</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8455395102500916</v>
+        <v>0.7994647622108459</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9069024324417114</v>
+        <v>0.828365683555603</v>
       </c>
       <c r="X18" t="n">
-        <v>0.8810880184173584</v>
+        <v>0.8305207490921021</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8645888566970825</v>
+        <v>0.8186362981796265</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.8926560878753662</v>
+        <v>0.824305534362793</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8618605136871338</v>
+        <v>0.8239538073539734</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8211671113967896</v>
+        <v>0.897186279296875</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8684271574020386</v>
+        <v>0.8272530436515808</v>
       </c>
     </row>
     <row r="19">
@@ -2148,7 +2148,7 @@
         <v>0.9006692171096802</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8322204947471619</v>
+        <v>0.8274298906326294</v>
       </c>
       <c r="K19" t="n">
         <v>0.8710378408432007</v>
@@ -2169,10 +2169,10 @@
         <v>0.8813589215278625</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8592532873153687</v>
+        <v>0.8416507244110107</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87009197473526</v>
+        <v>0.8214161396026611</v>
       </c>
       <c r="S19" t="n">
         <v>0.9999999403953552</v>
@@ -2239,7 +2239,7 @@
         <v>0.8911222219467163</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8391239643096924</v>
+        <v>0.8336665034294128</v>
       </c>
       <c r="K20" t="n">
         <v>0.9023727178573608</v>
@@ -2260,10 +2260,10 @@
         <v>0.9019486308097839</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8667904734611511</v>
+        <v>0.8364711999893188</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9034159183502197</v>
+        <v>0.8266108632087708</v>
       </c>
       <c r="S20" t="n">
         <v>0.8915920257568359</v>
@@ -2330,7 +2330,7 @@
         <v>0.9054946899414062</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8325496912002563</v>
+        <v>0.8291482925415039</v>
       </c>
       <c r="K21" t="n">
         <v>0.8823256492614746</v>
@@ -2351,10 +2351,10 @@
         <v>0.8909293413162231</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.88332200050354</v>
+        <v>0.8427741527557373</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8811439275741577</v>
+        <v>0.8321260213851929</v>
       </c>
       <c r="S21" t="n">
         <v>0.9023893475532532</v>
@@ -2421,7 +2421,7 @@
         <v>0.8542855381965637</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8171987533569336</v>
+        <v>0.8119673728942871</v>
       </c>
       <c r="K22" t="n">
         <v>0.8778689503669739</v>
@@ -2442,10 +2442,10 @@
         <v>0.8984862565994263</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8306186199188232</v>
+        <v>0.8257176876068115</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8455395102500916</v>
+        <v>0.7994647622108459</v>
       </c>
       <c r="S22" t="n">
         <v>0.8749428987503052</v>
@@ -2512,7 +2512,7 @@
         <v>0.9036498665809631</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8453735113143921</v>
+        <v>0.8405823707580566</v>
       </c>
       <c r="K23" t="n">
         <v>0.9212817549705505</v>
@@ -2533,10 +2533,10 @@
         <v>0.9150462746620178</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.8835150003433228</v>
+        <v>0.8499367833137512</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9069024324417114</v>
+        <v>0.828365683555603</v>
       </c>
       <c r="S23" t="n">
         <v>0.8950690031051636</v>
@@ -2603,7 +2603,7 @@
         <v>0.8795552849769592</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8302240967750549</v>
+        <v>0.8251742124557495</v>
       </c>
       <c r="K24" t="n">
         <v>0.9014301300048828</v>
@@ -2624,10 +2624,10 @@
         <v>0.8876562118530273</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8595641255378723</v>
+        <v>0.8467764854431152</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8810880184173584</v>
+        <v>0.8305207490921021</v>
       </c>
       <c r="S24" t="n">
         <v>0.8799763917922974</v>
@@ -2694,7 +2694,7 @@
         <v>0.8782399892807007</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8405318260192871</v>
+        <v>0.827221155166626</v>
       </c>
       <c r="K25" t="n">
         <v>0.9006924629211426</v>
@@ -2715,10 +2715,10 @@
         <v>0.9192123413085938</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8608036637306213</v>
+        <v>0.8399659395217896</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8645888566970825</v>
+        <v>0.8186362981796265</v>
       </c>
       <c r="S25" t="n">
         <v>0.8868472576141357</v>
@@ -2785,7 +2785,7 @@
         <v>0.9112921357154846</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8465471267700195</v>
+        <v>0.8362271785736084</v>
       </c>
       <c r="K26" t="n">
         <v>0.8756319880485535</v>
@@ -2806,10 +2806,10 @@
         <v>0.8921593427658081</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8739874362945557</v>
+        <v>0.8588438034057617</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8926560878753662</v>
+        <v>0.824305534362793</v>
       </c>
       <c r="S26" t="n">
         <v>0.9093791246414185</v>
@@ -2876,7 +2876,7 @@
         <v>0.8981694579124451</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8375923633575439</v>
+        <v>0.8342908024787903</v>
       </c>
       <c r="K27" t="n">
         <v>0.8725012540817261</v>
@@ -2897,10 +2897,10 @@
         <v>0.8949098587036133</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8623703718185425</v>
+        <v>0.8345358371734619</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8618605136871338</v>
+        <v>0.8239538073539734</v>
       </c>
       <c r="S27" t="n">
         <v>0.8760640621185303</v>
@@ -2967,7 +2967,7 @@
         <v>0.8332096338272095</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8891992568969727</v>
+        <v>0.8821119070053101</v>
       </c>
       <c r="K28" t="n">
         <v>0.817221999168396</v>
@@ -2988,10 +2988,10 @@
         <v>0.8217706680297852</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8068119287490845</v>
+        <v>0.8854494094848633</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8211671113967896</v>
+        <v>0.897186279296875</v>
       </c>
       <c r="S28" t="n">
         <v>0.8358195424079895</v>
@@ -3058,7 +3058,7 @@
         <v>0.8896946907043457</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8408675193786621</v>
+        <v>0.8334486484527588</v>
       </c>
       <c r="K29" t="n">
         <v>0.8965610265731812</v>
@@ -3079,10 +3079,10 @@
         <v>0.9206446409225464</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8646461963653564</v>
+        <v>0.8531848192214966</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8684271574020386</v>
+        <v>0.8272530436515808</v>
       </c>
       <c r="S29" t="n">
         <v>0.8798643350601196</v>

--- a/generated/teacher_teacher_similarity.xlsx
+++ b/generated/teacher_teacher_similarity.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung Duc Tuan</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -601,7 +601,7 @@
         <v>0.8951934576034546</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8302707672119141</v>
+        <v>0.9225988984107971</v>
       </c>
       <c r="K2" t="n">
         <v>0.9121062755584717</v>
@@ -622,10 +622,10 @@
         <v>0.9101829528808594</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8336291313171387</v>
+        <v>0.8557331562042236</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8343381881713867</v>
+        <v>0.9148001670837402</v>
       </c>
       <c r="S2" t="n">
         <v>0.8883686065673828</v>
@@ -692,7 +692,7 @@
         <v>0.8631153702735901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8289872407913208</v>
+        <v>0.858088493347168</v>
       </c>
       <c r="K3" t="n">
         <v>0.8384642601013184</v>
@@ -713,10 +713,10 @@
         <v>0.8673862218856812</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8335090279579163</v>
+        <v>0.8494427800178528</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8175127506256104</v>
+        <v>0.8339660167694092</v>
       </c>
       <c r="S3" t="n">
         <v>0.8419703245162964</v>
@@ -783,7 +783,7 @@
         <v>0.8535363674163818</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8349167704582214</v>
+        <v>0.8760606646537781</v>
       </c>
       <c r="K4" t="n">
         <v>0.8530595898628235</v>
@@ -804,10 +804,10 @@
         <v>0.8733971118927002</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8369334936141968</v>
+        <v>0.8564963936805725</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8352609276771545</v>
+        <v>0.8605788946151733</v>
       </c>
       <c r="S4" t="n">
         <v>0.8449867963790894</v>
@@ -874,7 +874,7 @@
         <v>0.8900558352470398</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8357346057891846</v>
+        <v>0.9175485372543335</v>
       </c>
       <c r="K5" t="n">
         <v>0.908711850643158</v>
@@ -895,10 +895,10 @@
         <v>0.893433153629303</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8382150530815125</v>
+        <v>0.8678715229034424</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8337386846542358</v>
+        <v>0.9103295207023621</v>
       </c>
       <c r="S5" t="n">
         <v>0.8785125017166138</v>
@@ -965,7 +965,7 @@
         <v>0.8921396732330322</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8341986536979675</v>
+        <v>0.9130096435546875</v>
       </c>
       <c r="K6" t="n">
         <v>0.8980830311775208</v>
@@ -986,10 +986,10 @@
         <v>0.8930953741073608</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8307888507843018</v>
+        <v>0.8595305681228638</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8262513875961304</v>
+        <v>0.8917438387870789</v>
       </c>
       <c r="S6" t="n">
         <v>0.8723194599151611</v>
@@ -1056,7 +1056,7 @@
         <v>0.9021725654602051</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8370206356048584</v>
+        <v>0.9073240160942078</v>
       </c>
       <c r="K7" t="n">
         <v>0.9011684060096741</v>
@@ -1077,10 +1077,10 @@
         <v>0.8969775438308716</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8332059383392334</v>
+        <v>0.8597217798233032</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8429336547851562</v>
+        <v>0.9027513861656189</v>
       </c>
       <c r="S7" t="n">
         <v>0.8932348489761353</v>
@@ -1147,7 +1147,7 @@
         <v>0.8745768666267395</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8441516160964966</v>
+        <v>0.8833758234977722</v>
       </c>
       <c r="K8" t="n">
         <v>0.8788844347000122</v>
@@ -1168,10 +1168,10 @@
         <v>0.8885284662246704</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8626000881195068</v>
+        <v>0.8680731058120728</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8523857593536377</v>
+        <v>0.8672974705696106</v>
       </c>
       <c r="S8" t="n">
         <v>0.8663286566734314</v>
@@ -1238,7 +1238,7 @@
         <v>0.9999998807907104</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8434658050537109</v>
+        <v>0.8979226350784302</v>
       </c>
       <c r="K9" t="n">
         <v>0.8714597821235657</v>
@@ -1259,10 +1259,10 @@
         <v>0.8861508369445801</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8431073427200317</v>
+        <v>0.872855544090271</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8250465393066406</v>
+        <v>0.8784716725349426</v>
       </c>
       <c r="S9" t="n">
         <v>0.9006692171096802</v>
@@ -1301,92 +1301,92 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung Duc Tuan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8302707672119141</v>
+        <v>0.9225988984107971</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8289872407913208</v>
+        <v>0.858088493347168</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8349167704582214</v>
+        <v>0.8760606646537781</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8357346057891846</v>
+        <v>0.9175485372543335</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8341986536979675</v>
+        <v>0.9130096435546875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8370206356048584</v>
+        <v>0.9073240160942078</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8441516160964966</v>
+        <v>0.8833758234977722</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8434658050537109</v>
+        <v>0.8979226350784302</v>
       </c>
       <c r="J10" t="n">
         <v>1.00000011920929</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8303543329238892</v>
+        <v>0.9280549287796021</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8460994958877563</v>
+        <v>0.9263849258422852</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8435174226760864</v>
+        <v>0.9013804197311401</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8366104364395142</v>
+        <v>0.8954148292541504</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8362822532653809</v>
+        <v>0.9002346992492676</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8321028351783752</v>
+        <v>0.9218416810035706</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9398021697998047</v>
+        <v>0.8918765783309937</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9279340505599976</v>
+        <v>0.9021685123443604</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8274298906326294</v>
+        <v>0.8973251581192017</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8336665034294128</v>
+        <v>0.9149646759033203</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8291482925415039</v>
+        <v>0.8970366716384888</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8119673728942871</v>
+        <v>0.8760872483253479</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8405823707580566</v>
+        <v>0.9307594895362854</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8251742124557495</v>
+        <v>0.8982971906661987</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.827221155166626</v>
+        <v>0.8961199522018433</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8362271785736084</v>
+        <v>0.9014552235603333</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8342908024787903</v>
+        <v>0.8956211805343628</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8821119070053101</v>
+        <v>0.825011134147644</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8334486484527588</v>
+        <v>0.9150675535202026</v>
       </c>
     </row>
     <row r="11">
@@ -1420,7 +1420,7 @@
         <v>0.8714597821235657</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8303543329238892</v>
+        <v>0.9280549287796021</v>
       </c>
       <c r="K11" t="n">
         <v>0.9999998807907104</v>
@@ -1441,10 +1441,10 @@
         <v>0.9071863889694214</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8479938507080078</v>
+        <v>0.8738576173782349</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8295843601226807</v>
+        <v>0.8863324522972107</v>
       </c>
       <c r="S11" t="n">
         <v>0.8710378408432007</v>
@@ -1511,7 +1511,7 @@
         <v>0.8997255563735962</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8460994958877563</v>
+        <v>0.9263849258422852</v>
       </c>
       <c r="K12" t="n">
         <v>0.905300498008728</v>
@@ -1532,10 +1532,10 @@
         <v>0.9211479425430298</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8533174991607666</v>
+        <v>0.8683022856712341</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8354157209396362</v>
+        <v>0.9069734811782837</v>
       </c>
       <c r="S12" t="n">
         <v>0.8914902806282043</v>
@@ -1602,7 +1602,7 @@
         <v>0.9117185473442078</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8435174226760864</v>
+        <v>0.9013804197311401</v>
       </c>
       <c r="K13" t="n">
         <v>0.8927918672561646</v>
@@ -1623,10 +1623,10 @@
         <v>0.915088951587677</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8506760597229004</v>
+        <v>0.8703169822692871</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8384671211242676</v>
+        <v>0.8780305981636047</v>
       </c>
       <c r="S13" t="n">
         <v>0.903888463973999</v>
@@ -1693,7 +1693,7 @@
         <v>0.8979413509368896</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8366104364395142</v>
+        <v>0.8954148292541504</v>
       </c>
       <c r="K14" t="n">
         <v>0.8723720908164978</v>
@@ -1714,10 +1714,10 @@
         <v>0.8959065675735474</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8447829484939575</v>
+        <v>0.8756363391876221</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8360897898674011</v>
+        <v>0.8884810209274292</v>
       </c>
       <c r="S14" t="n">
         <v>0.8714480400085449</v>
@@ -1784,7 +1784,7 @@
         <v>0.8949402570724487</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8362822532653809</v>
+        <v>0.9002346992492676</v>
       </c>
       <c r="K15" t="n">
         <v>0.8869379758834839</v>
@@ -1805,10 +1805,10 @@
         <v>0.9104539155960083</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8529775142669678</v>
+        <v>0.8715478181838989</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8333733081817627</v>
+        <v>0.8753183484077454</v>
       </c>
       <c r="S15" t="n">
         <v>0.8957282304763794</v>
@@ -1875,7 +1875,7 @@
         <v>0.8861508369445801</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8321028351783752</v>
+        <v>0.9218416810035706</v>
       </c>
       <c r="K16" t="n">
         <v>0.9071863889694214</v>
@@ -1896,10 +1896,10 @@
         <v>1.000000476837158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.847346305847168</v>
+        <v>0.8749116659164429</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8235707879066467</v>
+        <v>0.8724351525306702</v>
       </c>
       <c r="S16" t="n">
         <v>0.8813589215278625</v>
@@ -1938,183 +1938,183 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8336291313171387</v>
+        <v>0.8557331562042236</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8335090279579163</v>
+        <v>0.8494427800178528</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8369334936141968</v>
+        <v>0.8564963936805725</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8382150530815125</v>
+        <v>0.8678715229034424</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8307888507843018</v>
+        <v>0.8595305681228638</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8332059383392334</v>
+        <v>0.8597217798233032</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8626000881195068</v>
+        <v>0.8680731058120728</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8431073427200317</v>
+        <v>0.872855544090271</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9398021697998047</v>
+        <v>0.8918765783309937</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8479938507080078</v>
+        <v>0.8738576173782349</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8533174991607666</v>
+        <v>0.8683022856712341</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8506760597229004</v>
+        <v>0.8703169822692871</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8447829484939575</v>
+        <v>0.8756363391876221</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8529775142669678</v>
+        <v>0.8715478181838989</v>
       </c>
       <c r="P17" t="n">
-        <v>0.847346305847168</v>
+        <v>0.8749116659164429</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9999997615814209</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9344090223312378</v>
+        <v>0.8680868148803711</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8416507244110107</v>
+        <v>0.8592532873153687</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8364711999893188</v>
+        <v>0.8667904734611511</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8427741527557373</v>
+        <v>0.88332200050354</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8257176876068115</v>
+        <v>0.8306186199188232</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8499367833137512</v>
+        <v>0.8835150003433228</v>
       </c>
       <c r="X17" t="n">
-        <v>0.8467764854431152</v>
+        <v>0.8595641255378723</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8399659395217896</v>
+        <v>0.8608036637306213</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.8588438034057617</v>
+        <v>0.8739874362945557</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8345358371734619</v>
+        <v>0.8623703718185425</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8854494094848633</v>
+        <v>0.8068119287490845</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8531848192214966</v>
+        <v>0.8646461963653564</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8343381881713867</v>
+        <v>0.9148001670837402</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8175127506256104</v>
+        <v>0.8339660167694092</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8352609276771545</v>
+        <v>0.8605788946151733</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8337386846542358</v>
+        <v>0.9103295207023621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8262513875961304</v>
+        <v>0.8917438387870789</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8429336547851562</v>
+        <v>0.9027513861656189</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8523857593536377</v>
+        <v>0.8672974705696106</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8250465393066406</v>
+        <v>0.8784716725349426</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9279340505599976</v>
+        <v>0.9021685123443604</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8295843601226807</v>
+        <v>0.8863324522972107</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8354157209396362</v>
+        <v>0.9069734811782837</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8384671211242676</v>
+        <v>0.8780305981636047</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8360897898674011</v>
+        <v>0.8884810209274292</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8333733081817627</v>
+        <v>0.8753183484077454</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8235707879066467</v>
+        <v>0.8724351525306702</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9344090223312378</v>
+        <v>0.8680868148803711</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9999998807907104</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8214161396026611</v>
+        <v>0.87009197473526</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8266108632087708</v>
+        <v>0.9034159183502197</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8321260213851929</v>
+        <v>0.8811439275741577</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7994647622108459</v>
+        <v>0.8455395102500916</v>
       </c>
       <c r="W18" t="n">
-        <v>0.828365683555603</v>
+        <v>0.9069024324417114</v>
       </c>
       <c r="X18" t="n">
-        <v>0.8305207490921021</v>
+        <v>0.8810880184173584</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8186362981796265</v>
+        <v>0.8645888566970825</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.824305534362793</v>
+        <v>0.8926560878753662</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8239538073539734</v>
+        <v>0.8618605136871338</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.897186279296875</v>
+        <v>0.8211671113967896</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8272530436515808</v>
+        <v>0.8684271574020386</v>
       </c>
     </row>
     <row r="19">
@@ -2148,7 +2148,7 @@
         <v>0.9006692171096802</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8274298906326294</v>
+        <v>0.8973251581192017</v>
       </c>
       <c r="K19" t="n">
         <v>0.8710378408432007</v>
@@ -2169,10 +2169,10 @@
         <v>0.8813589215278625</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8416507244110107</v>
+        <v>0.8592532873153687</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214161396026611</v>
+        <v>0.87009197473526</v>
       </c>
       <c r="S19" t="n">
         <v>0.9999999403953552</v>
@@ -2239,7 +2239,7 @@
         <v>0.8911222219467163</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8336665034294128</v>
+        <v>0.9149646759033203</v>
       </c>
       <c r="K20" t="n">
         <v>0.9023727178573608</v>
@@ -2260,10 +2260,10 @@
         <v>0.9019486308097839</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8364711999893188</v>
+        <v>0.8667904734611511</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8266108632087708</v>
+        <v>0.9034159183502197</v>
       </c>
       <c r="S20" t="n">
         <v>0.8915920257568359</v>
@@ -2330,7 +2330,7 @@
         <v>0.9054946899414062</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8291482925415039</v>
+        <v>0.8970366716384888</v>
       </c>
       <c r="K21" t="n">
         <v>0.8823256492614746</v>
@@ -2351,10 +2351,10 @@
         <v>0.8909293413162231</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8427741527557373</v>
+        <v>0.88332200050354</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8321260213851929</v>
+        <v>0.8811439275741577</v>
       </c>
       <c r="S21" t="n">
         <v>0.9023893475532532</v>
@@ -2421,7 +2421,7 @@
         <v>0.8542855381965637</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8119673728942871</v>
+        <v>0.8760872483253479</v>
       </c>
       <c r="K22" t="n">
         <v>0.8778689503669739</v>
@@ -2442,10 +2442,10 @@
         <v>0.8984862565994263</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8257176876068115</v>
+        <v>0.8306186199188232</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7994647622108459</v>
+        <v>0.8455395102500916</v>
       </c>
       <c r="S22" t="n">
         <v>0.8749428987503052</v>
@@ -2512,7 +2512,7 @@
         <v>0.9036498665809631</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8405823707580566</v>
+        <v>0.9307594895362854</v>
       </c>
       <c r="K23" t="n">
         <v>0.9212817549705505</v>
@@ -2533,10 +2533,10 @@
         <v>0.9150462746620178</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.8499367833137512</v>
+        <v>0.8835150003433228</v>
       </c>
       <c r="R23" t="n">
-        <v>0.828365683555603</v>
+        <v>0.9069024324417114</v>
       </c>
       <c r="S23" t="n">
         <v>0.8950690031051636</v>
@@ -2603,7 +2603,7 @@
         <v>0.8795552849769592</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8251742124557495</v>
+        <v>0.8982971906661987</v>
       </c>
       <c r="K24" t="n">
         <v>0.9014301300048828</v>
@@ -2624,10 +2624,10 @@
         <v>0.8876562118530273</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8467764854431152</v>
+        <v>0.8595641255378723</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8305207490921021</v>
+        <v>0.8810880184173584</v>
       </c>
       <c r="S24" t="n">
         <v>0.8799763917922974</v>
@@ -2694,7 +2694,7 @@
         <v>0.8782399892807007</v>
       </c>
       <c r="J25" t="n">
-        <v>0.827221155166626</v>
+        <v>0.8961199522018433</v>
       </c>
       <c r="K25" t="n">
         <v>0.9006924629211426</v>
@@ -2715,10 +2715,10 @@
         <v>0.9192123413085938</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8399659395217896</v>
+        <v>0.8608036637306213</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8186362981796265</v>
+        <v>0.8645888566970825</v>
       </c>
       <c r="S25" t="n">
         <v>0.8868472576141357</v>
@@ -2785,7 +2785,7 @@
         <v>0.9112921357154846</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8362271785736084</v>
+        <v>0.9014552235603333</v>
       </c>
       <c r="K26" t="n">
         <v>0.8756319880485535</v>
@@ -2806,10 +2806,10 @@
         <v>0.8921593427658081</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8588438034057617</v>
+        <v>0.8739874362945557</v>
       </c>
       <c r="R26" t="n">
-        <v>0.824305534362793</v>
+        <v>0.8926560878753662</v>
       </c>
       <c r="S26" t="n">
         <v>0.9093791246414185</v>
@@ -2876,7 +2876,7 @@
         <v>0.8981694579124451</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8342908024787903</v>
+        <v>0.8956211805343628</v>
       </c>
       <c r="K27" t="n">
         <v>0.8725012540817261</v>
@@ -2897,10 +2897,10 @@
         <v>0.8949098587036133</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8345358371734619</v>
+        <v>0.8623703718185425</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8239538073539734</v>
+        <v>0.8618605136871338</v>
       </c>
       <c r="S27" t="n">
         <v>0.8760640621185303</v>
@@ -2967,7 +2967,7 @@
         <v>0.8332096338272095</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8821119070053101</v>
+        <v>0.825011134147644</v>
       </c>
       <c r="K28" t="n">
         <v>0.817221999168396</v>
@@ -2988,10 +2988,10 @@
         <v>0.8217706680297852</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8854494094848633</v>
+        <v>0.8068119287490845</v>
       </c>
       <c r="R28" t="n">
-        <v>0.897186279296875</v>
+        <v>0.8211671113967896</v>
       </c>
       <c r="S28" t="n">
         <v>0.8358195424079895</v>
@@ -3058,7 +3058,7 @@
         <v>0.8896946907043457</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8334486484527588</v>
+        <v>0.9150675535202026</v>
       </c>
       <c r="K29" t="n">
         <v>0.8965610265731812</v>
@@ -3079,10 +3079,10 @@
         <v>0.9206446409225464</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8531848192214966</v>
+        <v>0.8646461963653564</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8272530436515808</v>
+        <v>0.8684271574020386</v>
       </c>
       <c r="S29" t="n">
         <v>0.8798643350601196</v>
